--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_food_wholesalers.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_food_wholesalers.xlsx
@@ -1397,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1534,22 +1534,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07167845946352035</v>
+        <v>0.07153301331486153</v>
       </c>
       <c r="C2">
-        <v>400.5173568515463</v>
+        <v>398.4736347648201</v>
       </c>
       <c r="D2">
-        <v>394.2373568515463</v>
+        <v>396.4656347648202</v>
       </c>
       <c r="E2">
-        <v>-110.5</v>
+        <v>-106.228</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.272</v>
       </c>
       <c r="G2">
         <v>6.28</v>
@@ -1570,28 +1570,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2148816</v>
       </c>
       <c r="N2">
-        <v>36.30408163265306</v>
+        <v>36.08920003265306</v>
       </c>
       <c r="O2">
-        <v>9.076020408163265</v>
+        <v>9.022300008163265</v>
       </c>
       <c r="P2">
-        <v>27.22806122448979</v>
+        <v>27.0669000244898</v>
       </c>
       <c r="Q2">
-        <v>31.12806122448979</v>
+        <v>30.9669000244898</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07167845946352035</v>
+        <v>0.07187450839885004</v>
       </c>
       <c r="T2">
-        <v>0.5044193424952811</v>
+        <v>0.5082407011505483</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>168.9492335902798</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1616,22 +1616,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07153301331486153</v>
+        <v>0.07138756716620275</v>
       </c>
       <c r="C3">
-        <v>398.4736347648201</v>
+        <v>396.455244859033</v>
       </c>
       <c r="D3">
-        <v>396.4656347648202</v>
+        <v>398.719244859033</v>
       </c>
       <c r="E3">
-        <v>-106.228</v>
+        <v>-101.956</v>
       </c>
       <c r="F3">
-        <v>4.272</v>
+        <v>8.544</v>
       </c>
       <c r="G3">
         <v>6.28</v>
@@ -1652,28 +1652,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M3">
-        <v>0.2148816</v>
+        <v>0.4297632</v>
       </c>
       <c r="N3">
-        <v>36.08920003265306</v>
+        <v>35.87431843265306</v>
       </c>
       <c r="O3">
-        <v>9.022300008163265</v>
+        <v>8.968579608163264</v>
       </c>
       <c r="P3">
-        <v>27.0669000244898</v>
+        <v>26.90573882448979</v>
       </c>
       <c r="Q3">
-        <v>30.9669000244898</v>
+        <v>30.80573882448979</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07187450839885004</v>
+        <v>0.07207455833285994</v>
       </c>
       <c r="T3">
-        <v>0.5082407011505483</v>
+        <v>0.5121400467171476</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>168.9492335902798</v>
+        <v>84.47461679513987</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1698,22 +1698,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07138756716620275</v>
+        <v>0.07124212101754394</v>
       </c>
       <c r="C4">
-        <v>396.455244859033</v>
+        <v>394.462621587133</v>
       </c>
       <c r="D4">
-        <v>398.719244859033</v>
+        <v>400.998621587133</v>
       </c>
       <c r="E4">
-        <v>-101.956</v>
+        <v>-97.684</v>
       </c>
       <c r="F4">
-        <v>8.544</v>
+        <v>12.816</v>
       </c>
       <c r="G4">
         <v>6.28</v>
@@ -1734,28 +1734,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M4">
-        <v>0.4297632</v>
+        <v>0.6446447999999999</v>
       </c>
       <c r="N4">
-        <v>35.87431843265306</v>
+        <v>35.65943683265306</v>
       </c>
       <c r="O4">
-        <v>8.968579608163264</v>
+        <v>8.914859208163264</v>
       </c>
       <c r="P4">
-        <v>26.90573882448979</v>
+        <v>26.74457762448979</v>
       </c>
       <c r="Q4">
-        <v>30.80573882448979</v>
+        <v>30.64457762448979</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07207455833285994</v>
+        <v>0.07227873300777726</v>
       </c>
       <c r="T4">
-        <v>0.5121400467171476</v>
+        <v>0.5161197911614087</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>84.47461679513987</v>
+        <v>56.31641119675992</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1780,22 +1780,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07124212101754394</v>
+        <v>0.07109667486888513</v>
       </c>
       <c r="C5">
-        <v>394.462621587133</v>
+        <v>392.4962093938165</v>
       </c>
       <c r="D5">
-        <v>400.998621587133</v>
+        <v>403.3042093938166</v>
       </c>
       <c r="E5">
-        <v>-97.684</v>
+        <v>-93.41200000000001</v>
       </c>
       <c r="F5">
-        <v>12.816</v>
+        <v>17.088</v>
       </c>
       <c r="G5">
         <v>6.28</v>
@@ -1816,28 +1816,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M5">
-        <v>0.6446447999999999</v>
+        <v>0.8595264</v>
       </c>
       <c r="N5">
-        <v>35.65943683265306</v>
+        <v>35.44455523265306</v>
       </c>
       <c r="O5">
-        <v>8.914859208163264</v>
+        <v>8.861138808163265</v>
       </c>
       <c r="P5">
-        <v>26.74457762448979</v>
+        <v>26.58341642448979</v>
       </c>
       <c r="Q5">
-        <v>30.64457762448979</v>
+        <v>30.48341642448979</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07227873300777726</v>
+        <v>0.07248716132175535</v>
       </c>
       <c r="T5">
-        <v>0.5161197911614087</v>
+        <v>0.5201824469482587</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>56.31641119675992</v>
+        <v>42.23730839756994</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1862,22 +1862,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07109667486888513</v>
+        <v>0.07095122872022634</v>
       </c>
       <c r="C6">
-        <v>392.4962093938165</v>
+        <v>390.5564630044337</v>
       </c>
       <c r="D6">
-        <v>403.3042093938166</v>
+        <v>405.6364630044338</v>
       </c>
       <c r="E6">
-        <v>-93.41200000000001</v>
+        <v>-89.14</v>
       </c>
       <c r="F6">
-        <v>17.088</v>
+        <v>21.36</v>
       </c>
       <c r="G6">
         <v>6.28</v>
@@ -1898,28 +1898,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M6">
-        <v>0.8595264</v>
+        <v>1.074408</v>
       </c>
       <c r="N6">
-        <v>35.44455523265306</v>
+        <v>35.22967363265306</v>
       </c>
       <c r="O6">
-        <v>8.861138808163265</v>
+        <v>8.807418408163265</v>
       </c>
       <c r="P6">
-        <v>26.58341642448979</v>
+        <v>26.4222552244898</v>
       </c>
       <c r="Q6">
-        <v>30.48341642448979</v>
+        <v>30.32225522448979</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07248716132175535</v>
+        <v>0.07269997760023825</v>
       </c>
       <c r="T6">
-        <v>0.5201824469482587</v>
+        <v>0.5243306323306212</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>42.23730839756994</v>
+        <v>33.78984671805596</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1944,22 +1944,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07095122872022634</v>
+        <v>0.07080578257156754</v>
       </c>
       <c r="C7">
-        <v>390.5564630044337</v>
+        <v>388.6438477239769</v>
       </c>
       <c r="D7">
-        <v>405.6364630044338</v>
+        <v>407.9958477239769</v>
       </c>
       <c r="E7">
-        <v>-89.14</v>
+        <v>-84.86799999999999</v>
       </c>
       <c r="F7">
-        <v>21.36</v>
+        <v>25.632</v>
       </c>
       <c r="G7">
         <v>6.28</v>
@@ -1980,28 +1980,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M7">
-        <v>1.074408</v>
+        <v>1.2892896</v>
       </c>
       <c r="N7">
-        <v>35.22967363265306</v>
+        <v>35.01479203265306</v>
       </c>
       <c r="O7">
-        <v>8.807418408163265</v>
+        <v>8.753698008163266</v>
       </c>
       <c r="P7">
-        <v>26.4222552244898</v>
+        <v>26.2610940244898</v>
       </c>
       <c r="Q7">
-        <v>30.32225522448979</v>
+        <v>30.1610940244898</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07269997760023825</v>
+        <v>0.07291732188464632</v>
       </c>
       <c r="T7">
-        <v>0.5243306323306212</v>
+        <v>0.5285670769764381</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>33.78984671805596</v>
+        <v>28.15820559837996</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2026,22 +2026,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07080578257156754</v>
+        <v>0.07066033642290874</v>
       </c>
       <c r="C8">
-        <v>388.6438477239769</v>
+        <v>386.7588397465607</v>
       </c>
       <c r="D8">
-        <v>407.9958477239769</v>
+        <v>410.3828397465608</v>
       </c>
       <c r="E8">
-        <v>-84.86799999999999</v>
+        <v>-80.596</v>
       </c>
       <c r="F8">
-        <v>25.632</v>
+        <v>29.904</v>
       </c>
       <c r="G8">
         <v>6.28</v>
@@ -2062,28 +2062,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M8">
-        <v>1.2892896</v>
+        <v>1.5041712</v>
       </c>
       <c r="N8">
-        <v>35.01479203265306</v>
+        <v>34.79991043265306</v>
       </c>
       <c r="O8">
-        <v>8.753698008163266</v>
+        <v>8.699977608163264</v>
       </c>
       <c r="P8">
-        <v>26.2610940244898</v>
+        <v>26.09993282448979</v>
       </c>
       <c r="Q8">
-        <v>30.1610940244898</v>
+        <v>29.99993282448979</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07291732188464632</v>
+        <v>0.07313934023968681</v>
       </c>
       <c r="T8">
-        <v>0.5285670769764381</v>
+        <v>0.5328946279587243</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.15820559837996</v>
+        <v>24.1356047986114</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2108,22 +2108,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07066033642290873</v>
+        <v>0.07051489027424995</v>
       </c>
       <c r="C9">
-        <v>386.758839746561</v>
+        <v>384.9019264758343</v>
       </c>
       <c r="D9">
-        <v>410.382839746561</v>
+        <v>412.7979264758343</v>
       </c>
       <c r="E9">
-        <v>-80.596</v>
+        <v>-76.324</v>
       </c>
       <c r="F9">
-        <v>29.904</v>
+        <v>34.176</v>
       </c>
       <c r="G9">
         <v>6.28</v>
@@ -2144,28 +2144,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M9">
-        <v>1.5041712</v>
+        <v>1.7190528</v>
       </c>
       <c r="N9">
-        <v>34.79991043265306</v>
+        <v>34.58502883265306</v>
       </c>
       <c r="O9">
-        <v>8.699977608163264</v>
+        <v>8.646257208163265</v>
       </c>
       <c r="P9">
-        <v>26.09993282448979</v>
+        <v>25.9387716244898</v>
       </c>
       <c r="Q9">
-        <v>29.99993282448979</v>
+        <v>29.83877162448979</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07313934023968681</v>
+        <v>0.07336618508070646</v>
       </c>
       <c r="T9">
-        <v>0.5328946279587243</v>
+        <v>0.5373162561362778</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.13560479861139</v>
+        <v>21.11865419878497</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2190,22 +2190,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07051489027424995</v>
+        <v>0.07036944412559114</v>
       </c>
       <c r="C10">
-        <v>384.9019264758343</v>
+        <v>383.0736068567721</v>
       </c>
       <c r="D10">
-        <v>412.7979264758343</v>
+        <v>415.2416068567721</v>
       </c>
       <c r="E10">
-        <v>-76.324</v>
+        <v>-72.05199999999999</v>
       </c>
       <c r="F10">
-        <v>34.176</v>
+        <v>38.448</v>
       </c>
       <c r="G10">
         <v>6.28</v>
@@ -2226,28 +2226,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M10">
-        <v>1.7190528</v>
+        <v>1.9339344</v>
       </c>
       <c r="N10">
-        <v>34.58502883265306</v>
+        <v>34.37014723265306</v>
       </c>
       <c r="O10">
-        <v>8.646257208163265</v>
+        <v>8.592536808163265</v>
       </c>
       <c r="P10">
-        <v>25.9387716244898</v>
+        <v>25.77761042448979</v>
       </c>
       <c r="Q10">
-        <v>29.83877162448979</v>
+        <v>29.67761042448979</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07336618508070646</v>
+        <v>0.07359801552262762</v>
       </c>
       <c r="T10">
-        <v>0.5373162561362778</v>
+        <v>0.5418350629550959</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.11865419878497</v>
+        <v>18.77213706558664</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2272,22 +2272,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07036944412559114</v>
+        <v>0.07022399797693234</v>
       </c>
       <c r="C11">
-        <v>383.0736068567721</v>
+        <v>381.2743917193181</v>
       </c>
       <c r="D11">
-        <v>415.2416068567721</v>
+        <v>417.7143917193181</v>
       </c>
       <c r="E11">
-        <v>-72.05199999999999</v>
+        <v>-67.78</v>
       </c>
       <c r="F11">
-        <v>38.448</v>
+        <v>42.71999999999999</v>
       </c>
       <c r="G11">
         <v>6.28</v>
@@ -2308,28 +2308,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M11">
-        <v>1.9339344</v>
+        <v>2.148816</v>
       </c>
       <c r="N11">
-        <v>34.37014723265306</v>
+        <v>34.15526563265306</v>
       </c>
       <c r="O11">
-        <v>8.592536808163265</v>
+        <v>8.538816408163266</v>
       </c>
       <c r="P11">
-        <v>25.77761042448979</v>
+        <v>25.6164492244898</v>
       </c>
       <c r="Q11">
-        <v>29.67761042448979</v>
+        <v>29.5164492244898</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07359801552262762</v>
+        <v>0.07383499775214704</v>
       </c>
       <c r="T11">
-        <v>0.5418350629550959</v>
+        <v>0.5464542877032211</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.77213706558664</v>
+        <v>16.89492335902798</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07022399797693234</v>
+        <v>0.07007855182827352</v>
       </c>
       <c r="C12">
-        <v>381.274391719318</v>
+        <v>379.5048041343857</v>
       </c>
       <c r="D12">
-        <v>417.7143917193181</v>
+        <v>420.2168041343857</v>
       </c>
       <c r="E12">
-        <v>-67.78</v>
+        <v>-63.508</v>
       </c>
       <c r="F12">
-        <v>42.72</v>
+        <v>46.992</v>
       </c>
       <c r="G12">
         <v>6.28</v>
@@ -2390,28 +2390,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M12">
-        <v>2.148816</v>
+        <v>2.3636976</v>
       </c>
       <c r="N12">
-        <v>34.15526563265306</v>
+        <v>33.94038403265306</v>
       </c>
       <c r="O12">
-        <v>8.538816408163266</v>
+        <v>8.485096008163264</v>
       </c>
       <c r="P12">
-        <v>25.6164492244898</v>
+        <v>25.45528802448979</v>
       </c>
       <c r="Q12">
-        <v>29.5164492244898</v>
+        <v>29.35528802448979</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07383499775214704</v>
+        <v>0.07407730542502644</v>
       </c>
       <c r="T12">
-        <v>0.5464542877032211</v>
+        <v>0.5511773152546752</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.89492335902798</v>
+        <v>15.35902123547998</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2436,22 +2436,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07007855182827352</v>
+        <v>0.06993310567961473</v>
       </c>
       <c r="C13">
-        <v>379.5048041343857</v>
+        <v>377.7653797827274</v>
       </c>
       <c r="D13">
-        <v>420.2168041343857</v>
+        <v>422.7493797827274</v>
       </c>
       <c r="E13">
-        <v>-63.508</v>
+        <v>-59.236</v>
       </c>
       <c r="F13">
-        <v>46.992</v>
+        <v>51.264</v>
       </c>
       <c r="G13">
         <v>6.28</v>
@@ -2472,28 +2472,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M13">
-        <v>2.3636976</v>
+        <v>2.5785792</v>
       </c>
       <c r="N13">
-        <v>33.94038403265306</v>
+        <v>33.72550243265306</v>
       </c>
       <c r="O13">
-        <v>8.485096008163264</v>
+        <v>8.431375608163265</v>
       </c>
       <c r="P13">
-        <v>25.45528802448979</v>
+        <v>25.29412682448979</v>
       </c>
       <c r="Q13">
-        <v>29.35528802448979</v>
+        <v>29.19412682448979</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07407730542502644</v>
+        <v>0.07432512009047129</v>
       </c>
       <c r="T13">
-        <v>0.5511773152546752</v>
+        <v>0.5560076843413894</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.35902123547998</v>
+        <v>14.07910279918998</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2518,22 +2518,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06993310567961473</v>
+        <v>0.06978765953095593</v>
       </c>
       <c r="C14">
-        <v>377.7653797827274</v>
+        <v>376.0566673372279</v>
       </c>
       <c r="D14">
-        <v>422.7493797827274</v>
+        <v>425.3126673372279</v>
       </c>
       <c r="E14">
-        <v>-59.236</v>
+        <v>-54.964</v>
       </c>
       <c r="F14">
-        <v>51.264</v>
+        <v>55.536</v>
       </c>
       <c r="G14">
         <v>6.28</v>
@@ -2554,28 +2554,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M14">
-        <v>2.5785792</v>
+        <v>2.7934608</v>
       </c>
       <c r="N14">
-        <v>33.72550243265306</v>
+        <v>33.51062083265306</v>
       </c>
       <c r="O14">
-        <v>8.431375608163265</v>
+        <v>8.377655208163265</v>
       </c>
       <c r="P14">
-        <v>25.29412682448979</v>
+        <v>25.1329656244898</v>
       </c>
       <c r="Q14">
-        <v>29.19412682448979</v>
+        <v>29.03296562448979</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07432512009047129</v>
+        <v>0.07457863164477693</v>
       </c>
       <c r="T14">
-        <v>0.5560076843413894</v>
+        <v>0.5609490963956143</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.07910279918998</v>
+        <v>12.99609489155998</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2600,22 +2600,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06978765953095593</v>
+        <v>0.06979971338229712</v>
       </c>
       <c r="C15">
-        <v>376.0566673372279</v>
+        <v>371.571054133439</v>
       </c>
       <c r="D15">
-        <v>425.3126673372279</v>
+        <v>425.099054133439</v>
       </c>
       <c r="E15">
-        <v>-54.964</v>
+        <v>-50.69199999999999</v>
       </c>
       <c r="F15">
-        <v>55.536</v>
+        <v>59.80800000000001</v>
       </c>
       <c r="G15">
         <v>6.28</v>
@@ -2636,45 +2636,45 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M15">
-        <v>2.7934608</v>
+        <v>3.0980544</v>
       </c>
       <c r="N15">
-        <v>33.51062083265306</v>
+        <v>33.20602723265306</v>
       </c>
       <c r="O15">
-        <v>8.377655208163265</v>
+        <v>8.301506808163264</v>
       </c>
       <c r="P15">
-        <v>25.1329656244898</v>
+        <v>24.90452042448979</v>
       </c>
       <c r="Q15">
-        <v>29.03296562448979</v>
+        <v>28.80452042448979</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07457863164477693</v>
+        <v>0.07483803881662457</v>
       </c>
       <c r="T15">
-        <v>0.5609490963956143</v>
+        <v>0.5660054250092398</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>12.99609489155998</v>
+        <v>11.71834866187406</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2682,22 +2682,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06979971338229712</v>
+        <v>0.06966551723363834</v>
       </c>
       <c r="C16">
-        <v>371.571054133439</v>
+        <v>369.6893922645896</v>
       </c>
       <c r="D16">
-        <v>425.099054133439</v>
+        <v>427.4893922645896</v>
       </c>
       <c r="E16">
-        <v>-50.69199999999999</v>
+        <v>-46.41999999999999</v>
       </c>
       <c r="F16">
-        <v>59.80800000000001</v>
+        <v>64.08000000000001</v>
       </c>
       <c r="G16">
         <v>6.28</v>
@@ -2718,28 +2718,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M16">
-        <v>3.0980544</v>
+        <v>3.319344000000001</v>
       </c>
       <c r="N16">
-        <v>33.20602723265306</v>
+        <v>32.98473763265306</v>
       </c>
       <c r="O16">
-        <v>8.301506808163264</v>
+        <v>8.246184408163264</v>
       </c>
       <c r="P16">
-        <v>24.90452042448979</v>
+        <v>24.73855322448979</v>
       </c>
       <c r="Q16">
-        <v>28.80452042448979</v>
+        <v>28.63855322448979</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07483803881662457</v>
+        <v>0.07510354968663334</v>
       </c>
       <c r="T16">
-        <v>0.5660054250092398</v>
+        <v>0.571180726060833</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.71834866187406</v>
+        <v>10.93712541774913</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2764,22 +2764,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06966551723363834</v>
+        <v>0.06953132108497953</v>
       </c>
       <c r="C17">
-        <v>369.6893922645896</v>
+        <v>367.8347642191039</v>
       </c>
       <c r="D17">
-        <v>427.4893922645896</v>
+        <v>429.906764219104</v>
       </c>
       <c r="E17">
-        <v>-46.42</v>
+        <v>-42.148</v>
       </c>
       <c r="F17">
-        <v>64.08</v>
+        <v>68.352</v>
       </c>
       <c r="G17">
         <v>6.28</v>
@@ -2800,28 +2800,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M17">
-        <v>3.319344</v>
+        <v>3.5406336</v>
       </c>
       <c r="N17">
-        <v>32.98473763265306</v>
+        <v>32.76344803265306</v>
       </c>
       <c r="O17">
-        <v>8.246184408163264</v>
+        <v>8.190862008163265</v>
       </c>
       <c r="P17">
-        <v>24.73855322448979</v>
+        <v>24.57258602448979</v>
       </c>
       <c r="Q17">
-        <v>28.63855322448979</v>
+        <v>28.47258602448979</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07510354968663334</v>
+        <v>0.07537538224402325</v>
       </c>
       <c r="T17">
-        <v>0.571180726060833</v>
+        <v>0.5764792485660355</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.93712541774913</v>
+        <v>10.25355507913981</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2846,22 +2846,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06953132108497953</v>
+        <v>0.06961387493632074</v>
       </c>
       <c r="C18">
-        <v>367.8347642191039</v>
+        <v>362.0724372899996</v>
       </c>
       <c r="D18">
-        <v>429.906764219104</v>
+        <v>428.4164372899996</v>
       </c>
       <c r="E18">
-        <v>-42.148</v>
+        <v>-37.87599999999999</v>
       </c>
       <c r="F18">
-        <v>68.352</v>
+        <v>72.62400000000001</v>
       </c>
       <c r="G18">
         <v>6.28</v>
@@ -2882,45 +2882,45 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M18">
-        <v>3.5406336</v>
+        <v>3.885384000000001</v>
       </c>
       <c r="N18">
-        <v>32.76344803265306</v>
+        <v>32.41869763265306</v>
       </c>
       <c r="O18">
-        <v>8.190862008163265</v>
+        <v>8.104674408163264</v>
       </c>
       <c r="P18">
-        <v>24.57258602448979</v>
+        <v>24.31402322448979</v>
       </c>
       <c r="Q18">
-        <v>28.47258602448979</v>
+        <v>28.21402322448979</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07537538224402325</v>
+        <v>0.07565376498351896</v>
       </c>
       <c r="T18">
-        <v>0.5764792485660355</v>
+        <v>0.5819054463123273</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>10.25355507913981</v>
+        <v>9.343756404168301</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2928,22 +2928,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06961387493632074</v>
+        <v>0.06949242878766192</v>
       </c>
       <c r="C19">
-        <v>362.0724372899996</v>
+        <v>359.9964775017189</v>
       </c>
       <c r="D19">
-        <v>428.4164372899996</v>
+        <v>430.612477501719</v>
       </c>
       <c r="E19">
-        <v>-37.87599999999999</v>
+        <v>-33.604</v>
       </c>
       <c r="F19">
-        <v>72.62400000000001</v>
+        <v>76.896</v>
       </c>
       <c r="G19">
         <v>6.28</v>
@@ -2964,28 +2964,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M19">
-        <v>3.885384000000001</v>
+        <v>4.113936</v>
       </c>
       <c r="N19">
-        <v>32.41869763265306</v>
+        <v>32.19014563265306</v>
       </c>
       <c r="O19">
-        <v>8.104674408163264</v>
+        <v>8.047536408163264</v>
       </c>
       <c r="P19">
-        <v>24.31402322448979</v>
+        <v>24.14260922448979</v>
       </c>
       <c r="Q19">
-        <v>28.21402322448979</v>
+        <v>28.04260922448979</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07565376498351896</v>
+        <v>0.07593893754592917</v>
       </c>
       <c r="T19">
-        <v>0.5819054463123273</v>
+        <v>0.5874639903451139</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.343756404168301</v>
+        <v>8.824658826158952</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3010,22 +3010,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06949242878766193</v>
+        <v>0.06937098263900314</v>
       </c>
       <c r="C20">
-        <v>359.9964775017187</v>
+        <v>357.943147285577</v>
       </c>
       <c r="D20">
-        <v>430.6124775017187</v>
+        <v>432.831147285577</v>
       </c>
       <c r="E20">
-        <v>-33.604</v>
+        <v>-29.33200000000001</v>
       </c>
       <c r="F20">
-        <v>76.896</v>
+        <v>81.16799999999999</v>
       </c>
       <c r="G20">
         <v>6.28</v>
@@ -3046,28 +3046,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M20">
-        <v>4.113936</v>
+        <v>4.342487999999999</v>
       </c>
       <c r="N20">
-        <v>32.19014563265306</v>
+        <v>31.96159363265306</v>
       </c>
       <c r="O20">
-        <v>8.047536408163264</v>
+        <v>7.990398408163265</v>
       </c>
       <c r="P20">
-        <v>24.14260922448979</v>
+        <v>23.97119522448979</v>
       </c>
       <c r="Q20">
-        <v>28.04260922448979</v>
+        <v>27.87119522448979</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07593893754592917</v>
+        <v>0.0762311514061767</v>
       </c>
       <c r="T20">
-        <v>0.5874639903451139</v>
+        <v>0.5931597823787103</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.824658826158952</v>
+        <v>8.360203098466378</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3092,22 +3092,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06937098263900314</v>
+        <v>0.06924953649034434</v>
       </c>
       <c r="C21">
-        <v>357.943147285577</v>
+        <v>355.91279824013</v>
       </c>
       <c r="D21">
-        <v>432.831147285577</v>
+        <v>435.07279824013</v>
       </c>
       <c r="E21">
-        <v>-29.33200000000001</v>
+        <v>-25.06</v>
       </c>
       <c r="F21">
-        <v>81.16799999999999</v>
+        <v>85.44</v>
       </c>
       <c r="G21">
         <v>6.28</v>
@@ -3128,28 +3128,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M21">
-        <v>4.342487999999999</v>
+        <v>4.57104</v>
       </c>
       <c r="N21">
-        <v>31.96159363265306</v>
+        <v>31.73304163265306</v>
       </c>
       <c r="O21">
-        <v>7.990398408163265</v>
+        <v>7.933260408163265</v>
       </c>
       <c r="P21">
-        <v>23.97119522448979</v>
+        <v>23.7997812244898</v>
       </c>
       <c r="Q21">
-        <v>27.87119522448979</v>
+        <v>27.69978122448979</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0762311514061767</v>
+        <v>0.07653067061293041</v>
       </c>
       <c r="T21">
-        <v>0.5931597823787103</v>
+        <v>0.5989979692131463</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.360203098466378</v>
+        <v>7.942192943543057</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3174,22 +3174,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06924953649034434</v>
+        <v>0.06925409034168553</v>
       </c>
       <c r="C22">
-        <v>355.91279824013</v>
+        <v>351.5563244098973</v>
       </c>
       <c r="D22">
-        <v>435.07279824013</v>
+        <v>434.9883244098974</v>
       </c>
       <c r="E22">
-        <v>-25.06</v>
+        <v>-20.788</v>
       </c>
       <c r="F22">
-        <v>85.44</v>
+        <v>89.712</v>
       </c>
       <c r="G22">
         <v>6.28</v>
@@ -3210,45 +3210,45 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M22">
-        <v>4.57104</v>
+        <v>4.8713616</v>
       </c>
       <c r="N22">
-        <v>31.73304163265306</v>
+        <v>31.43272003265306</v>
       </c>
       <c r="O22">
-        <v>7.933260408163265</v>
+        <v>7.858180008163265</v>
       </c>
       <c r="P22">
-        <v>23.7997812244898</v>
+        <v>23.57454002448979</v>
       </c>
       <c r="Q22">
-        <v>27.69978122448979</v>
+        <v>27.47454002448979</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07653067061293041</v>
+        <v>0.07683777258441206</v>
       </c>
       <c r="T22">
-        <v>0.5989979692131463</v>
+        <v>0.6049839582459225</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.942192943543057</v>
+        <v>7.452553231247103</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3256,22 +3256,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06925409034168553</v>
+        <v>0.06913864419302672</v>
       </c>
       <c r="C23">
-        <v>351.5563244098973</v>
+        <v>349.4360229554229</v>
       </c>
       <c r="D23">
-        <v>434.9883244098974</v>
+        <v>437.1400229554229</v>
       </c>
       <c r="E23">
-        <v>-20.78800000000001</v>
+        <v>-16.51600000000001</v>
       </c>
       <c r="F23">
-        <v>89.71199999999999</v>
+        <v>93.98399999999999</v>
       </c>
       <c r="G23">
         <v>6.28</v>
@@ -3292,28 +3292,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M23">
-        <v>4.871361599999999</v>
+        <v>5.1033312</v>
       </c>
       <c r="N23">
-        <v>31.43272003265306</v>
+        <v>31.20075043265306</v>
       </c>
       <c r="O23">
-        <v>7.858180008163265</v>
+        <v>7.800187608163265</v>
       </c>
       <c r="P23">
-        <v>23.57454002448979</v>
+        <v>23.4005628244898</v>
       </c>
       <c r="Q23">
-        <v>27.47454002448979</v>
+        <v>27.30056282448979</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07683777258441206</v>
+        <v>0.07715274896541888</v>
       </c>
       <c r="T23">
-        <v>0.6049839582459225</v>
+        <v>0.6111234341769751</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.452553231247104</v>
+        <v>7.113800811644963</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3338,22 +3338,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06913864419302672</v>
+        <v>0.06902319804436793</v>
       </c>
       <c r="C24">
-        <v>349.4360229554229</v>
+        <v>347.3371143607668</v>
       </c>
       <c r="D24">
-        <v>437.1400229554229</v>
+        <v>439.3131143607668</v>
       </c>
       <c r="E24">
-        <v>-16.51600000000001</v>
+        <v>-12.244</v>
       </c>
       <c r="F24">
-        <v>93.98399999999999</v>
+        <v>98.256</v>
       </c>
       <c r="G24">
         <v>6.28</v>
@@ -3374,28 +3374,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M24">
-        <v>5.1033312</v>
+        <v>5.3353008</v>
       </c>
       <c r="N24">
-        <v>31.20075043265306</v>
+        <v>30.96878083265306</v>
       </c>
       <c r="O24">
-        <v>7.800187608163265</v>
+        <v>7.742195208163265</v>
       </c>
       <c r="P24">
-        <v>23.4005628244898</v>
+        <v>23.22658562448979</v>
       </c>
       <c r="Q24">
-        <v>27.30056282448979</v>
+        <v>27.12658562448979</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07715274896541888</v>
+        <v>0.07747590655112718</v>
       </c>
       <c r="T24">
-        <v>0.6111234341769751</v>
+        <v>0.6174223770153279</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.113800811644963</v>
+        <v>6.804505124182138</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3420,22 +3420,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06902319804436793</v>
+        <v>0.06890775189570914</v>
       </c>
       <c r="C25">
-        <v>347.3371143607668</v>
+        <v>345.2599192616135</v>
       </c>
       <c r="D25">
-        <v>439.3131143607668</v>
+        <v>441.5079192616136</v>
       </c>
       <c r="E25">
-        <v>-12.244</v>
+        <v>-7.971999999999994</v>
       </c>
       <c r="F25">
-        <v>98.256</v>
+        <v>102.528</v>
       </c>
       <c r="G25">
         <v>6.28</v>
@@ -3456,28 +3456,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M25">
-        <v>5.3353008</v>
+        <v>5.567270400000001</v>
       </c>
       <c r="N25">
-        <v>30.96878083265306</v>
+        <v>30.73681123265306</v>
       </c>
       <c r="O25">
-        <v>7.742195208163265</v>
+        <v>7.684202808163264</v>
       </c>
       <c r="P25">
-        <v>23.22658562448979</v>
+        <v>23.05260842448979</v>
       </c>
       <c r="Q25">
-        <v>27.12658562448979</v>
+        <v>26.95260842448979</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07747590655112718</v>
+        <v>0.0778075682838278</v>
       </c>
       <c r="T25">
-        <v>0.6174223770153279</v>
+        <v>0.6238870815073214</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.804505124182138</v>
+        <v>6.520984077341214</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3502,22 +3502,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06890775189570914</v>
+        <v>0.06879230574705032</v>
       </c>
       <c r="C26">
-        <v>345.2599192616135</v>
+        <v>343.2047647333931</v>
       </c>
       <c r="D26">
-        <v>441.5079192616136</v>
+        <v>443.7247647333931</v>
       </c>
       <c r="E26">
-        <v>-7.972000000000008</v>
+        <v>-3.700000000000003</v>
       </c>
       <c r="F26">
-        <v>102.528</v>
+        <v>106.8</v>
       </c>
       <c r="G26">
         <v>6.28</v>
@@ -3538,28 +3538,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M26">
-        <v>5.5672704</v>
+        <v>5.79924</v>
       </c>
       <c r="N26">
-        <v>30.73681123265306</v>
+        <v>30.50484163265306</v>
       </c>
       <c r="O26">
-        <v>7.684202808163265</v>
+        <v>7.626210408163264</v>
       </c>
       <c r="P26">
-        <v>23.0526084244898</v>
+        <v>22.87863122448979</v>
       </c>
       <c r="Q26">
-        <v>26.9526084244898</v>
+        <v>26.77863122448979</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0778075682838278</v>
+        <v>0.07814807432940044</v>
       </c>
       <c r="T26">
-        <v>0.6238870815073214</v>
+        <v>0.6305241781191013</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.520984077341216</v>
+        <v>6.260144714247566</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3584,22 +3584,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06879230574705032</v>
+        <v>0.06887185959839152</v>
       </c>
       <c r="C27">
-        <v>343.2047647333931</v>
+        <v>337.4027617520785</v>
       </c>
       <c r="D27">
-        <v>443.7247647333931</v>
+        <v>442.1947617520785</v>
       </c>
       <c r="E27">
-        <v>-3.700000000000003</v>
+        <v>0.5720000000000027</v>
       </c>
       <c r="F27">
-        <v>106.8</v>
+        <v>111.072</v>
       </c>
       <c r="G27">
         <v>6.28</v>
@@ -3620,45 +3620,45 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M27">
-        <v>5.79924</v>
+        <v>6.1422816</v>
       </c>
       <c r="N27">
-        <v>30.50484163265306</v>
+        <v>30.16180003265306</v>
       </c>
       <c r="O27">
-        <v>7.626210408163264</v>
+        <v>7.540450008163265</v>
       </c>
       <c r="P27">
-        <v>22.87863122448979</v>
+        <v>22.62135002448979</v>
       </c>
       <c r="Q27">
-        <v>26.77863122448979</v>
+        <v>26.52135002448979</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07814807432940044</v>
+        <v>0.07849778324106962</v>
       </c>
       <c r="T27">
-        <v>0.6305241781191013</v>
+        <v>0.637340655720389</v>
       </c>
       <c r="U27">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.260144714247566</v>
+        <v>5.910520551948165</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3666,22 +3666,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06887185959839152</v>
+        <v>0.06876391344973273</v>
       </c>
       <c r="C28">
-        <v>337.4027617520785</v>
+        <v>335.2093805202913</v>
       </c>
       <c r="D28">
-        <v>442.1947617520785</v>
+        <v>444.2733805202914</v>
       </c>
       <c r="E28">
-        <v>0.5720000000000027</v>
+        <v>4.844000000000008</v>
       </c>
       <c r="F28">
-        <v>111.072</v>
+        <v>115.344</v>
       </c>
       <c r="G28">
         <v>6.28</v>
@@ -3702,28 +3702,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M28">
-        <v>6.1422816</v>
+        <v>6.378523200000001</v>
       </c>
       <c r="N28">
-        <v>30.16180003265306</v>
+        <v>29.92555843265306</v>
       </c>
       <c r="O28">
-        <v>7.540450008163265</v>
+        <v>7.481389608163265</v>
       </c>
       <c r="P28">
-        <v>22.62135002448979</v>
+        <v>22.44416882448979</v>
       </c>
       <c r="Q28">
-        <v>26.52135002448979</v>
+        <v>26.34416882448979</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07849778324106962</v>
+        <v>0.07885707321881195</v>
       </c>
       <c r="T28">
-        <v>0.637340655720389</v>
+        <v>0.6443438861326708</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.910520551948165</v>
+        <v>5.691612383357492</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3748,22 +3748,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06876391344973273</v>
+        <v>0.06865596730107393</v>
       </c>
       <c r="C29">
-        <v>335.2093805202913</v>
+        <v>333.0356334512245</v>
       </c>
       <c r="D29">
-        <v>444.2733805202914</v>
+        <v>446.3716334512245</v>
       </c>
       <c r="E29">
-        <v>4.844000000000008</v>
+        <v>9.116000000000014</v>
       </c>
       <c r="F29">
-        <v>115.344</v>
+        <v>119.616</v>
       </c>
       <c r="G29">
         <v>6.28</v>
@@ -3784,28 +3784,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M29">
-        <v>6.378523200000001</v>
+        <v>6.614764800000001</v>
       </c>
       <c r="N29">
-        <v>29.92555843265306</v>
+        <v>29.68931683265306</v>
       </c>
       <c r="O29">
-        <v>7.481389608163265</v>
+        <v>7.422329208163265</v>
       </c>
       <c r="P29">
-        <v>22.44416882448979</v>
+        <v>22.26698762448979</v>
       </c>
       <c r="Q29">
-        <v>26.34416882448979</v>
+        <v>26.16698762448979</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07885707321881195</v>
+        <v>0.07922634347371378</v>
       </c>
       <c r="T29">
-        <v>0.6443438861326708</v>
+        <v>0.6515416507230715</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.691612383357492</v>
+        <v>5.488340512523296</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3830,22 +3830,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06865596730107393</v>
+        <v>0.06854802115241512</v>
       </c>
       <c r="C30">
-        <v>333.0356334512245</v>
+        <v>330.8818000547616</v>
       </c>
       <c r="D30">
-        <v>446.3716334512245</v>
+        <v>448.4898000547616</v>
       </c>
       <c r="E30">
-        <v>9.116000000000014</v>
+        <v>13.38800000000001</v>
       </c>
       <c r="F30">
-        <v>119.616</v>
+        <v>123.888</v>
       </c>
       <c r="G30">
         <v>6.28</v>
@@ -3866,28 +3866,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M30">
-        <v>6.614764800000001</v>
+        <v>6.8510064</v>
       </c>
       <c r="N30">
-        <v>29.68931683265306</v>
+        <v>29.45307523265306</v>
       </c>
       <c r="O30">
-        <v>7.422329208163265</v>
+        <v>7.363268808163265</v>
       </c>
       <c r="P30">
-        <v>22.26698762448979</v>
+        <v>22.08980642448979</v>
       </c>
       <c r="Q30">
-        <v>26.16698762448979</v>
+        <v>25.98980642448979</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07922634347371378</v>
+        <v>0.07960601570762693</v>
       </c>
       <c r="T30">
-        <v>0.6515416507230715</v>
+        <v>0.658942169245596</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.488340512523296</v>
+        <v>5.299087391401804</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3912,22 +3912,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06854802115241512</v>
+        <v>0.06844007500375632</v>
       </c>
       <c r="C31">
-        <v>330.8818000547616</v>
+        <v>328.7481651715131</v>
       </c>
       <c r="D31">
-        <v>448.4898000547616</v>
+        <v>450.628165171513</v>
       </c>
       <c r="E31">
-        <v>13.38799999999999</v>
+        <v>17.66</v>
       </c>
       <c r="F31">
-        <v>123.888</v>
+        <v>128.16</v>
       </c>
       <c r="G31">
         <v>6.28</v>
@@ -3948,28 +3948,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M31">
-        <v>6.8510064</v>
+        <v>7.087248</v>
       </c>
       <c r="N31">
-        <v>29.45307523265306</v>
+        <v>29.21683363265306</v>
       </c>
       <c r="O31">
-        <v>7.363268808163265</v>
+        <v>7.304208408163265</v>
       </c>
       <c r="P31">
-        <v>22.08980642448979</v>
+        <v>21.91262522448979</v>
       </c>
       <c r="Q31">
-        <v>25.98980642448979</v>
+        <v>25.81262522448979</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07960601570762693</v>
+        <v>0.07999653571965189</v>
       </c>
       <c r="T31">
-        <v>0.658942169245596</v>
+        <v>0.6665541311544786</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.299087391401804</v>
+        <v>5.122451145021744</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3994,22 +3994,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06844007500375632</v>
+        <v>0.06833212885509751</v>
       </c>
       <c r="C32">
-        <v>328.7481651715131</v>
+        <v>326.6350191005081</v>
       </c>
       <c r="D32">
-        <v>450.628165171513</v>
+        <v>452.7870191005081</v>
       </c>
       <c r="E32">
-        <v>17.66</v>
+        <v>21.93199999999999</v>
       </c>
       <c r="F32">
-        <v>128.16</v>
+        <v>132.432</v>
       </c>
       <c r="G32">
         <v>6.28</v>
@@ -4030,28 +4030,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M32">
-        <v>7.087248</v>
+        <v>7.323489599999999</v>
       </c>
       <c r="N32">
-        <v>29.21683363265306</v>
+        <v>28.98059203265306</v>
       </c>
       <c r="O32">
-        <v>7.304208408163265</v>
+        <v>7.245148008163265</v>
       </c>
       <c r="P32">
-        <v>21.91262522448979</v>
+        <v>21.73544402448979</v>
       </c>
       <c r="Q32">
-        <v>25.81262522448979</v>
+        <v>25.63544402448979</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07999653571965189</v>
+        <v>0.08039837515231524</v>
       </c>
       <c r="T32">
-        <v>0.6665541311544786</v>
+        <v>0.6743867296404301</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.122451145021744</v>
+        <v>4.957210785504913</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4076,22 +4076,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06833212885509751</v>
+        <v>0.06822418270643871</v>
       </c>
       <c r="C33">
-        <v>326.6350191005081</v>
+        <v>324.5426577305735</v>
       </c>
       <c r="D33">
-        <v>452.7870191005081</v>
+        <v>454.9666577305736</v>
       </c>
       <c r="E33">
-        <v>21.93199999999999</v>
+        <v>26.20400000000001</v>
       </c>
       <c r="F33">
-        <v>132.432</v>
+        <v>136.704</v>
       </c>
       <c r="G33">
         <v>6.28</v>
@@ -4112,28 +4112,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M33">
-        <v>7.323489599999999</v>
+        <v>7.559731200000001</v>
       </c>
       <c r="N33">
-        <v>28.98059203265306</v>
+        <v>28.74435043265306</v>
       </c>
       <c r="O33">
-        <v>7.245148008163265</v>
+        <v>7.186087608163264</v>
       </c>
       <c r="P33">
-        <v>21.73544402448979</v>
+        <v>21.55826282448979</v>
       </c>
       <c r="Q33">
-        <v>25.63544402448979</v>
+        <v>25.45826282448979</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08039837515231524</v>
+        <v>0.08081203339182164</v>
       </c>
       <c r="T33">
-        <v>0.6743867296404301</v>
+        <v>0.6824496986700862</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.957210785504913</v>
+        <v>4.802297948457884</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4158,22 +4158,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06822418270643871</v>
+        <v>0.06811623655777992</v>
       </c>
       <c r="C34">
-        <v>324.5426577305735</v>
+        <v>322.4713826755265</v>
       </c>
       <c r="D34">
-        <v>454.9666577305736</v>
+        <v>457.1673826755265</v>
       </c>
       <c r="E34">
-        <v>26.20400000000001</v>
+        <v>30.476</v>
       </c>
       <c r="F34">
-        <v>136.704</v>
+        <v>140.976</v>
       </c>
       <c r="G34">
         <v>6.28</v>
@@ -4194,28 +4194,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M34">
-        <v>7.559731200000001</v>
+        <v>7.7959728</v>
       </c>
       <c r="N34">
-        <v>28.74435043265306</v>
+        <v>28.50810883265306</v>
       </c>
       <c r="O34">
-        <v>7.186087608163264</v>
+        <v>7.127027208163264</v>
       </c>
       <c r="P34">
-        <v>21.55826282448979</v>
+        <v>21.38108162448979</v>
       </c>
       <c r="Q34">
-        <v>25.45826282448979</v>
+        <v>25.28108162448979</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08081203339182164</v>
+        <v>0.08123803963847749</v>
       </c>
       <c r="T34">
-        <v>0.6824496986700862</v>
+        <v>0.6907533533424186</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.802297948457884</v>
+        <v>4.656773768201584</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4240,22 +4240,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06811623655777992</v>
+        <v>0.06800829040912111</v>
       </c>
       <c r="C35">
-        <v>322.4713826755265</v>
+        <v>320.4215014133101</v>
       </c>
       <c r="D35">
-        <v>457.1673826755265</v>
+        <v>459.3895014133101</v>
       </c>
       <c r="E35">
-        <v>30.476</v>
+        <v>34.74800000000002</v>
       </c>
       <c r="F35">
-        <v>140.976</v>
+        <v>145.248</v>
       </c>
       <c r="G35">
         <v>6.28</v>
@@ -4276,28 +4276,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M35">
-        <v>7.7959728</v>
+        <v>8.032214400000001</v>
       </c>
       <c r="N35">
-        <v>28.50810883265306</v>
+        <v>28.27186723265306</v>
       </c>
       <c r="O35">
-        <v>7.127027208163264</v>
+        <v>7.067966808163265</v>
       </c>
       <c r="P35">
-        <v>21.38108162448979</v>
+        <v>21.2039004244898</v>
       </c>
       <c r="Q35">
-        <v>25.28108162448979</v>
+        <v>25.10390042448979</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08123803963847749</v>
+        <v>0.08167695516533502</v>
       </c>
       <c r="T35">
-        <v>0.6907533533424186</v>
+        <v>0.6993086339139125</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.656773768201584</v>
+        <v>4.519809833842714</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4322,22 +4322,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06800829040912111</v>
+        <v>0.06855659426046232</v>
       </c>
       <c r="C36">
-        <v>320.4215014133101</v>
+        <v>305.0808401713131</v>
       </c>
       <c r="D36">
-        <v>459.3895014133101</v>
+        <v>448.3208401713131</v>
       </c>
       <c r="E36">
-        <v>34.74800000000002</v>
+        <v>39.02000000000001</v>
       </c>
       <c r="F36">
-        <v>145.248</v>
+        <v>149.52</v>
       </c>
       <c r="G36">
         <v>6.28</v>
@@ -4358,45 +4358,45 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M36">
-        <v>8.032214400000001</v>
+        <v>8.642256000000001</v>
       </c>
       <c r="N36">
-        <v>28.27186723265306</v>
+        <v>27.66182563265306</v>
       </c>
       <c r="O36">
-        <v>7.067966808163265</v>
+        <v>6.915456408163264</v>
       </c>
       <c r="P36">
-        <v>21.2039004244898</v>
+        <v>20.74636922448979</v>
       </c>
       <c r="Q36">
-        <v>25.10390042448979</v>
+        <v>24.64636922448979</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08167695516533502</v>
+        <v>0.08212937578532664</v>
       </c>
       <c r="T36">
-        <v>0.6993086339139125</v>
+        <v>0.7081271538876062</v>
       </c>
       <c r="U36">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.519809833842714</v>
+        <v>4.200764433806757</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4404,22 +4404,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06855659426046232</v>
+        <v>0.06846739811180351</v>
       </c>
       <c r="C37">
-        <v>305.0808401713131</v>
+        <v>302.5729814331165</v>
       </c>
       <c r="D37">
-        <v>448.3208401713131</v>
+        <v>450.0849814331166</v>
       </c>
       <c r="E37">
-        <v>39.02000000000001</v>
+        <v>43.292</v>
       </c>
       <c r="F37">
-        <v>149.52</v>
+        <v>153.792</v>
       </c>
       <c r="G37">
         <v>6.28</v>
@@ -4440,28 +4440,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M37">
-        <v>8.642256000000001</v>
+        <v>8.8891776</v>
       </c>
       <c r="N37">
-        <v>27.66182563265306</v>
+        <v>27.41490403265306</v>
       </c>
       <c r="O37">
-        <v>6.915456408163264</v>
+        <v>6.853726008163265</v>
       </c>
       <c r="P37">
-        <v>20.74636922448979</v>
+        <v>20.5611780244898</v>
       </c>
       <c r="Q37">
-        <v>24.64636922448979</v>
+        <v>24.46117802448979</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08212937578532664</v>
+        <v>0.082595934549693</v>
       </c>
       <c r="T37">
-        <v>0.7081271538876062</v>
+        <v>0.7172212526104778</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.200764433806757</v>
+        <v>4.084076532867682</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4486,22 +4486,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06846739811180351</v>
+        <v>0.06934945196314472</v>
       </c>
       <c r="C38">
-        <v>302.5729814331165</v>
+        <v>281.4428739949805</v>
       </c>
       <c r="D38">
-        <v>450.0849814331166</v>
+        <v>433.2268739949805</v>
       </c>
       <c r="E38">
-        <v>43.292</v>
+        <v>47.56399999999999</v>
       </c>
       <c r="F38">
-        <v>153.792</v>
+        <v>158.064</v>
       </c>
       <c r="G38">
         <v>6.28</v>
@@ -4522,45 +4522,45 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M38">
-        <v>8.8891776</v>
+        <v>9.6893232</v>
       </c>
       <c r="N38">
-        <v>27.41490403265306</v>
+        <v>26.61475843265306</v>
       </c>
       <c r="O38">
-        <v>6.853726008163265</v>
+        <v>6.653689608163265</v>
       </c>
       <c r="P38">
-        <v>20.5611780244898</v>
+        <v>19.96106882448979</v>
       </c>
       <c r="Q38">
-        <v>24.46117802448979</v>
+        <v>23.86106882448979</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.082595934549693</v>
+        <v>0.08307730470340431</v>
       </c>
       <c r="T38">
-        <v>0.7172212526104778</v>
+        <v>0.7266040528801073</v>
       </c>
       <c r="U38">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.084076532867682</v>
+        <v>3.746812948984203</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4568,22 +4568,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06934945196314472</v>
+        <v>0.06928650581448592</v>
       </c>
       <c r="C39">
-        <v>281.4428739949805</v>
+        <v>278.3319646837733</v>
       </c>
       <c r="D39">
-        <v>433.2268739949805</v>
+        <v>434.3879646837733</v>
       </c>
       <c r="E39">
-        <v>47.56399999999999</v>
+        <v>51.83599999999998</v>
       </c>
       <c r="F39">
-        <v>158.064</v>
+        <v>162.336</v>
       </c>
       <c r="G39">
         <v>6.28</v>
@@ -4604,28 +4604,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M39">
-        <v>9.6893232</v>
+        <v>9.9511968</v>
       </c>
       <c r="N39">
-        <v>26.61475843265306</v>
+        <v>26.35288483265306</v>
       </c>
       <c r="O39">
-        <v>6.653689608163265</v>
+        <v>6.588221208163265</v>
       </c>
       <c r="P39">
-        <v>19.96106882448979</v>
+        <v>19.7646636244898</v>
       </c>
       <c r="Q39">
-        <v>23.86106882448979</v>
+        <v>23.66466362448979</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08307730470340431</v>
+        <v>0.08357420292659018</v>
       </c>
       <c r="T39">
-        <v>0.7266040528801073</v>
+        <v>0.7362895241261764</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.746812948984203</v>
+        <v>3.648212608221462</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4650,22 +4650,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06928650581448592</v>
+        <v>0.06922355966582712</v>
       </c>
       <c r="C40">
-        <v>278.3319646837733</v>
+        <v>275.2272957722444</v>
       </c>
       <c r="D40">
-        <v>434.3879646837733</v>
+        <v>435.5552957722444</v>
       </c>
       <c r="E40">
-        <v>51.83599999999998</v>
+        <v>56.108</v>
       </c>
       <c r="F40">
-        <v>162.336</v>
+        <v>166.608</v>
       </c>
       <c r="G40">
         <v>6.28</v>
@@ -4686,28 +4686,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M40">
-        <v>9.9511968</v>
+        <v>10.2130704</v>
       </c>
       <c r="N40">
-        <v>26.35288483265306</v>
+        <v>26.09101123265306</v>
       </c>
       <c r="O40">
-        <v>6.588221208163265</v>
+        <v>6.522752808163265</v>
       </c>
       <c r="P40">
-        <v>19.7646636244898</v>
+        <v>19.56825842448979</v>
       </c>
       <c r="Q40">
-        <v>23.66466362448979</v>
+        <v>23.46825842448979</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08357420292659018</v>
+        <v>0.08408739289479855</v>
       </c>
       <c r="T40">
-        <v>0.7362895241261764</v>
+        <v>0.746292551806543</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.648212608221462</v>
+        <v>3.554668695190142</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4732,22 +4732,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06922355966582712</v>
+        <v>0.07000061351716833</v>
       </c>
       <c r="C41">
-        <v>275.2272957722444</v>
+        <v>256.9701164373577</v>
       </c>
       <c r="D41">
-        <v>435.5552957722444</v>
+        <v>421.5701164373577</v>
       </c>
       <c r="E41">
-        <v>56.108</v>
+        <v>60.38</v>
       </c>
       <c r="F41">
-        <v>166.608</v>
+        <v>170.88</v>
       </c>
       <c r="G41">
         <v>6.28</v>
@@ -4768,45 +4768,45 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M41">
-        <v>10.2130704</v>
+        <v>10.953408</v>
       </c>
       <c r="N41">
-        <v>26.09101123265306</v>
+        <v>25.35067363265306</v>
       </c>
       <c r="O41">
-        <v>6.522752808163265</v>
+        <v>6.337668408163265</v>
       </c>
       <c r="P41">
-        <v>19.56825842448979</v>
+        <v>19.0130052244898</v>
       </c>
       <c r="Q41">
-        <v>23.46825842448979</v>
+        <v>22.91300522448979</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08408739289479855</v>
+        <v>0.08461768919528052</v>
       </c>
       <c r="T41">
-        <v>0.746292551806543</v>
+        <v>0.7566290137429217</v>
       </c>
       <c r="U41">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.554668695190142</v>
+        <v>3.314409691728187</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4814,22 +4814,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07000061351716833</v>
+        <v>0.06995866736850952</v>
       </c>
       <c r="C42">
-        <v>256.9701164373577</v>
+        <v>253.4300791116418</v>
       </c>
       <c r="D42">
-        <v>421.5701164373577</v>
+        <v>422.3020791116418</v>
       </c>
       <c r="E42">
-        <v>60.38</v>
+        <v>64.65200000000002</v>
       </c>
       <c r="F42">
-        <v>170.88</v>
+        <v>175.152</v>
       </c>
       <c r="G42">
         <v>6.28</v>
@@ -4850,28 +4850,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M42">
-        <v>10.953408</v>
+        <v>11.2272432</v>
       </c>
       <c r="N42">
-        <v>25.35067363265306</v>
+        <v>25.07683843265306</v>
       </c>
       <c r="O42">
-        <v>6.337668408163265</v>
+        <v>6.269209608163264</v>
       </c>
       <c r="P42">
-        <v>19.0130052244898</v>
+        <v>18.80762882448979</v>
       </c>
       <c r="Q42">
-        <v>22.91300522448979</v>
+        <v>22.70762882448979</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08461768919528052</v>
+        <v>0.08516596164154155</v>
       </c>
       <c r="T42">
-        <v>0.7566290137429217</v>
+        <v>0.7673158642195167</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.314409691728187</v>
+        <v>3.233570430954328</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4896,22 +4896,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06995866736850952</v>
+        <v>0.06991672121985071</v>
       </c>
       <c r="C43">
-        <v>253.4300791116418</v>
+        <v>249.8925879873658</v>
       </c>
       <c r="D43">
-        <v>422.3020791116418</v>
+        <v>423.0365879873658</v>
       </c>
       <c r="E43">
-        <v>64.65200000000002</v>
+        <v>68.92400000000001</v>
       </c>
       <c r="F43">
-        <v>175.152</v>
+        <v>179.424</v>
       </c>
       <c r="G43">
         <v>6.28</v>
@@ -4932,28 +4932,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M43">
-        <v>11.2272432</v>
+        <v>11.5010784</v>
       </c>
       <c r="N43">
-        <v>25.07683843265306</v>
+        <v>24.80300323265306</v>
       </c>
       <c r="O43">
-        <v>6.269209608163264</v>
+        <v>6.200750808163265</v>
       </c>
       <c r="P43">
-        <v>18.80762882448979</v>
+        <v>18.60225242448979</v>
       </c>
       <c r="Q43">
-        <v>22.70762882448979</v>
+        <v>22.50225242448979</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08516596164154155</v>
+        <v>0.08573314003422536</v>
       </c>
       <c r="T43">
-        <v>0.7673158642195167</v>
+        <v>0.7783712267815114</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.233570430954328</v>
+        <v>3.156580658788749</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4978,22 +4978,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06991672121985071</v>
+        <v>0.06987477507119191</v>
       </c>
       <c r="C44">
-        <v>249.8925879873658</v>
+        <v>246.3576563734817</v>
       </c>
       <c r="D44">
-        <v>423.0365879873658</v>
+        <v>423.7736563734817</v>
       </c>
       <c r="E44">
-        <v>68.92399999999998</v>
+        <v>73.196</v>
       </c>
       <c r="F44">
-        <v>179.424</v>
+        <v>183.696</v>
       </c>
       <c r="G44">
         <v>6.28</v>
@@ -5014,28 +5014,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M44">
-        <v>11.5010784</v>
+        <v>11.7749136</v>
       </c>
       <c r="N44">
-        <v>24.80300323265306</v>
+        <v>24.52916803265306</v>
       </c>
       <c r="O44">
-        <v>6.200750808163265</v>
+        <v>6.132292008163264</v>
       </c>
       <c r="P44">
-        <v>18.6022524244898</v>
+        <v>18.39687602448979</v>
       </c>
       <c r="Q44">
-        <v>22.5022524244898</v>
+        <v>22.29687602448979</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08573314003422536</v>
+        <v>0.08632021942314369</v>
       </c>
       <c r="T44">
-        <v>0.7783712267815114</v>
+        <v>0.7898144968018216</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.15658065878875</v>
+        <v>3.083171806258779</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5060,22 +5060,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06987477507119191</v>
+        <v>0.06983282892253311</v>
       </c>
       <c r="C45">
-        <v>246.3576563734817</v>
+        <v>242.8252976718585</v>
       </c>
       <c r="D45">
-        <v>423.7736563734817</v>
+        <v>424.5132976718585</v>
       </c>
       <c r="E45">
-        <v>73.196</v>
+        <v>77.46799999999999</v>
       </c>
       <c r="F45">
-        <v>183.696</v>
+        <v>187.968</v>
       </c>
       <c r="G45">
         <v>6.28</v>
@@ -5096,28 +5096,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M45">
-        <v>11.7749136</v>
+        <v>12.0487488</v>
       </c>
       <c r="N45">
-        <v>24.52916803265306</v>
+        <v>24.25533283265306</v>
       </c>
       <c r="O45">
-        <v>6.132292008163264</v>
+        <v>6.063833208163265</v>
       </c>
       <c r="P45">
-        <v>18.39687602448979</v>
+        <v>18.19149962448979</v>
       </c>
       <c r="Q45">
-        <v>22.29687602448979</v>
+        <v>22.09149962448979</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08632021942314369</v>
+        <v>0.08692826593309483</v>
       </c>
       <c r="T45">
-        <v>0.7898144968018216</v>
+        <v>0.8016664550371432</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.083171806258779</v>
+        <v>3.013099719752898</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5142,22 +5142,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06983282892253311</v>
+        <v>0.07242338277387431</v>
       </c>
       <c r="C46">
-        <v>242.8252976718585</v>
+        <v>197.2465799053786</v>
       </c>
       <c r="D46">
-        <v>424.5132976718585</v>
+        <v>383.2065799053786</v>
       </c>
       <c r="E46">
-        <v>77.46799999999999</v>
+        <v>81.74000000000001</v>
       </c>
       <c r="F46">
-        <v>187.968</v>
+        <v>192.24</v>
       </c>
       <c r="G46">
         <v>6.28</v>
@@ -5178,45 +5178,45 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M46">
-        <v>12.0487488</v>
+        <v>13.822056</v>
       </c>
       <c r="N46">
-        <v>24.25533283265306</v>
+        <v>22.48202563265306</v>
       </c>
       <c r="O46">
-        <v>6.063833208163265</v>
+        <v>5.620506408163264</v>
       </c>
       <c r="P46">
-        <v>18.19149962448979</v>
+        <v>16.86151922448979</v>
       </c>
       <c r="Q46">
-        <v>22.09149962448979</v>
+        <v>20.76151922448979</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08692826593309483</v>
+        <v>0.087558423225226</v>
       </c>
       <c r="T46">
-        <v>0.8016664550371432</v>
+        <v>0.8139493935719307</v>
       </c>
       <c r="U46">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.013099719752898</v>
+        <v>2.626532668703777</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5224,22 +5224,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07242338277387431</v>
+        <v>0.0724399366252155</v>
       </c>
       <c r="C47">
-        <v>197.2465799053786</v>
+        <v>192.7364582894767</v>
       </c>
       <c r="D47">
-        <v>383.2065799053786</v>
+        <v>382.9684582894768</v>
       </c>
       <c r="E47">
-        <v>81.74000000000001</v>
+        <v>86.012</v>
       </c>
       <c r="F47">
-        <v>192.24</v>
+        <v>196.512</v>
       </c>
       <c r="G47">
         <v>6.28</v>
@@ -5260,28 +5260,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M47">
-        <v>13.822056</v>
+        <v>14.1292128</v>
       </c>
       <c r="N47">
-        <v>22.48202563265306</v>
+        <v>22.17486883265306</v>
       </c>
       <c r="O47">
-        <v>5.620506408163264</v>
+        <v>5.543717208163264</v>
       </c>
       <c r="P47">
-        <v>16.86151922448979</v>
+        <v>16.63115162448979</v>
       </c>
       <c r="Q47">
-        <v>20.76151922448979</v>
+        <v>20.53115162448979</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.087558423225226</v>
+        <v>0.08821191967632501</v>
       </c>
       <c r="T47">
-        <v>0.8139493935719307</v>
+        <v>0.8266872557561551</v>
       </c>
       <c r="U47">
         <v>0.07190000000000001</v>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.626532668703777</v>
+        <v>2.569434132427608</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5306,22 +5306,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0724399366252155</v>
+        <v>0.07245649047655671</v>
       </c>
       <c r="C48">
-        <v>192.7364582894767</v>
+        <v>188.2266324236722</v>
       </c>
       <c r="D48">
-        <v>382.9684582894768</v>
+        <v>382.7306324236723</v>
       </c>
       <c r="E48">
-        <v>86.012</v>
+        <v>90.28400000000002</v>
       </c>
       <c r="F48">
-        <v>196.512</v>
+        <v>200.784</v>
       </c>
       <c r="G48">
         <v>6.28</v>
@@ -5342,28 +5342,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M48">
-        <v>14.1292128</v>
+        <v>14.4363696</v>
       </c>
       <c r="N48">
-        <v>22.17486883265306</v>
+        <v>21.86771203265306</v>
       </c>
       <c r="O48">
-        <v>5.543717208163264</v>
+        <v>5.466928008163264</v>
       </c>
       <c r="P48">
-        <v>16.63115162448979</v>
+        <v>16.40078402448979</v>
       </c>
       <c r="Q48">
-        <v>20.53115162448979</v>
+        <v>20.30078402448979</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08821191967632501</v>
+        <v>0.08889007637086171</v>
       </c>
       <c r="T48">
-        <v>0.8266872557561551</v>
+        <v>0.8399057919850671</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.569434132427608</v>
+        <v>2.514765321099361</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5388,22 +5388,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07245649047655671</v>
+        <v>0.07387704432789791</v>
       </c>
       <c r="C49">
-        <v>188.2266324236722</v>
+        <v>164.5904334158913</v>
       </c>
       <c r="D49">
-        <v>382.7306324236723</v>
+        <v>363.3664334158914</v>
       </c>
       <c r="E49">
-        <v>90.28400000000002</v>
+        <v>94.55600000000001</v>
       </c>
       <c r="F49">
-        <v>200.784</v>
+        <v>205.056</v>
       </c>
       <c r="G49">
         <v>6.28</v>
@@ -5424,45 +5424,45 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M49">
-        <v>14.4363696</v>
+        <v>15.5432448</v>
       </c>
       <c r="N49">
-        <v>21.86771203265306</v>
+        <v>20.76083683265306</v>
       </c>
       <c r="O49">
-        <v>5.466928008163264</v>
+        <v>5.190209208163264</v>
       </c>
       <c r="P49">
-        <v>16.40078402448979</v>
+        <v>15.57062762448979</v>
       </c>
       <c r="Q49">
-        <v>20.30078402448979</v>
+        <v>19.47062762448979</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08889007637086171</v>
+        <v>0.08959431601518827</v>
       </c>
       <c r="T49">
-        <v>0.8399057919850671</v>
+        <v>0.8536327334535526</v>
       </c>
       <c r="U49">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.514765321099361</v>
+        <v>2.335682291554274</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5470,22 +5470,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07387704432789791</v>
+        <v>0.07392284817923911</v>
       </c>
       <c r="C50">
-        <v>164.5904334158914</v>
+        <v>159.7266163285008</v>
       </c>
       <c r="D50">
-        <v>363.3664334158914</v>
+        <v>362.7746163285008</v>
       </c>
       <c r="E50">
-        <v>94.55599999999998</v>
+        <v>98.828</v>
       </c>
       <c r="F50">
-        <v>205.056</v>
+        <v>209.328</v>
       </c>
       <c r="G50">
         <v>6.28</v>
@@ -5506,28 +5506,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M50">
-        <v>15.5432448</v>
+        <v>15.8670624</v>
       </c>
       <c r="N50">
-        <v>20.76083683265306</v>
+        <v>20.43701923265306</v>
       </c>
       <c r="O50">
-        <v>5.190209208163265</v>
+        <v>5.109254808163264</v>
       </c>
       <c r="P50">
-        <v>15.57062762448979</v>
+        <v>15.32776442448979</v>
       </c>
       <c r="Q50">
-        <v>19.47062762448979</v>
+        <v>19.22776442448979</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08959431601518827</v>
+        <v>0.09032617290046882</v>
       </c>
       <c r="T50">
-        <v>0.8536327334535526</v>
+        <v>0.8678979863521747</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.335682291554274</v>
+        <v>2.28801530601235</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5552,22 +5552,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07392284817923911</v>
+        <v>0.07396865203058031</v>
       </c>
       <c r="C51">
-        <v>159.7266163285008</v>
+        <v>154.864723898482</v>
       </c>
       <c r="D51">
-        <v>362.7746163285008</v>
+        <v>362.184723898482</v>
       </c>
       <c r="E51">
-        <v>98.828</v>
+        <v>103.1</v>
       </c>
       <c r="F51">
-        <v>209.328</v>
+        <v>213.6</v>
       </c>
       <c r="G51">
         <v>6.28</v>
@@ -5588,28 +5588,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M51">
-        <v>15.8670624</v>
+        <v>16.19088</v>
       </c>
       <c r="N51">
-        <v>20.43701923265306</v>
+        <v>20.11320163265306</v>
       </c>
       <c r="O51">
-        <v>5.109254808163264</v>
+        <v>5.028300408163265</v>
       </c>
       <c r="P51">
-        <v>15.32776442448979</v>
+        <v>15.08490122448979</v>
       </c>
       <c r="Q51">
-        <v>19.22776442448979</v>
+        <v>18.98490122448979</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09032617290046882</v>
+        <v>0.09108730406116061</v>
       </c>
       <c r="T51">
-        <v>0.8678979863521747</v>
+        <v>0.8827338493667419</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.28801530601235</v>
+        <v>2.242254999892103</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5634,22 +5634,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07396865203058031</v>
+        <v>0.0740144558819215</v>
       </c>
       <c r="C52">
-        <v>154.864723898482</v>
+        <v>150.0047467522658</v>
       </c>
       <c r="D52">
-        <v>362.184723898482</v>
+        <v>361.5967467522658</v>
       </c>
       <c r="E52">
-        <v>103.1</v>
+        <v>107.372</v>
       </c>
       <c r="F52">
-        <v>213.6</v>
+        <v>217.872</v>
       </c>
       <c r="G52">
         <v>6.28</v>
@@ -5670,28 +5670,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M52">
-        <v>16.19088</v>
+        <v>16.5146976</v>
       </c>
       <c r="N52">
-        <v>20.11320163265306</v>
+        <v>19.78938403265306</v>
       </c>
       <c r="O52">
-        <v>5.028300408163265</v>
+        <v>4.947346008163264</v>
       </c>
       <c r="P52">
-        <v>15.08490122448979</v>
+        <v>14.84203802448979</v>
       </c>
       <c r="Q52">
-        <v>18.98490122448979</v>
+        <v>18.74203802448979</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09108730406116061</v>
+        <v>0.09187950179983981</v>
       </c>
       <c r="T52">
-        <v>0.8827338493667419</v>
+        <v>0.898175257810475</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.242254999892103</v>
+        <v>2.198289215580493</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5716,22 +5716,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0740144558819215</v>
+        <v>0.0740602597332627</v>
       </c>
       <c r="C53">
-        <v>150.0047467522658</v>
+        <v>145.1466755770526</v>
       </c>
       <c r="D53">
-        <v>361.5967467522658</v>
+        <v>361.0106755770526</v>
       </c>
       <c r="E53">
-        <v>107.372</v>
+        <v>111.644</v>
       </c>
       <c r="F53">
-        <v>217.872</v>
+        <v>222.144</v>
       </c>
       <c r="G53">
         <v>6.28</v>
@@ -5752,28 +5752,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M53">
-        <v>16.5146976</v>
+        <v>16.8385152</v>
       </c>
       <c r="N53">
-        <v>19.78938403265306</v>
+        <v>19.46556643265306</v>
       </c>
       <c r="O53">
-        <v>4.947346008163264</v>
+        <v>4.866391608163264</v>
       </c>
       <c r="P53">
-        <v>14.84203802448979</v>
+        <v>14.59917482448979</v>
       </c>
       <c r="Q53">
-        <v>18.74203802448979</v>
+        <v>18.49917482448979</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09187950179983981</v>
+        <v>0.09270470777763062</v>
       </c>
       <c r="T53">
-        <v>0.898175257810475</v>
+        <v>0.914260058272697</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5790,7 +5790,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.198289215580493</v>
+        <v>2.156014422973176</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5798,22 +5798,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0740602597332627</v>
+        <v>0.07410606358460391</v>
       </c>
       <c r="C54">
-        <v>145.1466755770526</v>
+        <v>140.290501120322</v>
       </c>
       <c r="D54">
-        <v>361.0106755770526</v>
+        <v>360.426501120322</v>
       </c>
       <c r="E54">
-        <v>111.644</v>
+        <v>115.916</v>
       </c>
       <c r="F54">
-        <v>222.144</v>
+        <v>226.416</v>
       </c>
       <c r="G54">
         <v>6.28</v>
@@ -5834,28 +5834,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M54">
-        <v>16.8385152</v>
+        <v>17.1623328</v>
       </c>
       <c r="N54">
-        <v>19.46556643265306</v>
+        <v>19.14174883265306</v>
       </c>
       <c r="O54">
-        <v>4.866391608163264</v>
+        <v>4.785437208163264</v>
       </c>
       <c r="P54">
-        <v>14.59917482448979</v>
+        <v>14.35631162448979</v>
       </c>
       <c r="Q54">
-        <v>18.49917482448979</v>
+        <v>18.25631162448979</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09270470777763062</v>
+        <v>0.09356502890341256</v>
       </c>
       <c r="T54">
-        <v>0.914260058272697</v>
+        <v>0.9310293183290561</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.156014422973176</v>
+        <v>2.115334905558588</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5880,22 +5880,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07410606358460391</v>
+        <v>0.0741518674359451</v>
       </c>
       <c r="C55">
-        <v>140.290501120322</v>
+        <v>135.4362141893451</v>
       </c>
       <c r="D55">
-        <v>360.426501120322</v>
+        <v>359.8442141893451</v>
       </c>
       <c r="E55">
-        <v>115.916</v>
+        <v>120.188</v>
       </c>
       <c r="F55">
-        <v>226.416</v>
+        <v>230.688</v>
       </c>
       <c r="G55">
         <v>6.28</v>
@@ -5916,28 +5916,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M55">
-        <v>17.1623328</v>
+        <v>17.4861504</v>
       </c>
       <c r="N55">
-        <v>19.14174883265306</v>
+        <v>18.81793123265306</v>
       </c>
       <c r="O55">
-        <v>4.785437208163264</v>
+        <v>4.704482808163264</v>
       </c>
       <c r="P55">
-        <v>14.35631162448979</v>
+        <v>14.11344842448979</v>
       </c>
       <c r="Q55">
-        <v>18.25631162448979</v>
+        <v>18.01344842448979</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09356502890341256</v>
+        <v>0.09446275529553283</v>
       </c>
       <c r="T55">
-        <v>0.9310293183290561</v>
+        <v>0.9485276766487352</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.115334905558588</v>
+        <v>2.076162036937133</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5962,22 +5962,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0741518674359451</v>
+        <v>0.0741976712872863</v>
       </c>
       <c r="C56">
-        <v>135.4362141893451</v>
+        <v>130.583805650702</v>
       </c>
       <c r="D56">
-        <v>359.8442141893451</v>
+        <v>359.263805650702</v>
       </c>
       <c r="E56">
-        <v>120.188</v>
+        <v>124.46</v>
       </c>
       <c r="F56">
-        <v>230.688</v>
+        <v>234.96</v>
       </c>
       <c r="G56">
         <v>6.28</v>
@@ -5998,28 +5998,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M56">
-        <v>17.4861504</v>
+        <v>17.809968</v>
       </c>
       <c r="N56">
-        <v>18.81793123265306</v>
+        <v>18.49411363265306</v>
       </c>
       <c r="O56">
-        <v>4.704482808163264</v>
+        <v>4.623528408163264</v>
       </c>
       <c r="P56">
-        <v>14.11344842448979</v>
+        <v>13.87058522448979</v>
       </c>
       <c r="Q56">
-        <v>18.01344842448979</v>
+        <v>17.77058522448979</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09446275529553283</v>
+        <v>0.095400380638414</v>
       </c>
       <c r="T56">
-        <v>0.9485276766487352</v>
+        <v>0.9668037397826222</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.076162036937133</v>
+        <v>2.038413636265548</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6044,22 +6044,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0741976712872863</v>
+        <v>0.0742434751386275</v>
       </c>
       <c r="C57">
-        <v>130.583805650702</v>
+        <v>125.7332664298052</v>
       </c>
       <c r="D57">
-        <v>359.263805650702</v>
+        <v>358.6852664298052</v>
       </c>
       <c r="E57">
-        <v>124.46</v>
+        <v>128.732</v>
       </c>
       <c r="F57">
-        <v>234.96</v>
+        <v>239.232</v>
       </c>
       <c r="G57">
         <v>6.28</v>
@@ -6080,28 +6080,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M57">
-        <v>17.809968</v>
+        <v>18.1337856</v>
       </c>
       <c r="N57">
-        <v>18.49411363265306</v>
+        <v>18.17029603265306</v>
       </c>
       <c r="O57">
-        <v>4.623528408163264</v>
+        <v>4.542574008163264</v>
       </c>
       <c r="P57">
-        <v>13.87058522448979</v>
+        <v>13.62772202448979</v>
       </c>
       <c r="Q57">
-        <v>17.77058522448979</v>
+        <v>17.52772202448979</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.095400380638414</v>
+        <v>0.0963806253150625</v>
       </c>
       <c r="T57">
-        <v>0.9668037397826222</v>
+        <v>0.9859105330589585</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -6118,7 +6118,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.038413636265548</v>
+        <v>2.002013392760806</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6126,22 +6126,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0742434751386275</v>
+        <v>0.0803597789899687</v>
       </c>
       <c r="C58">
-        <v>125.7332664298052</v>
+        <v>57.98203882476923</v>
       </c>
       <c r="D58">
-        <v>358.6852664298052</v>
+        <v>295.2060388247693</v>
       </c>
       <c r="E58">
-        <v>128.732</v>
+        <v>133.004</v>
       </c>
       <c r="F58">
-        <v>239.232</v>
+        <v>243.504</v>
       </c>
       <c r="G58">
         <v>6.28</v>
@@ -6162,45 +6162,45 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M58">
-        <v>18.1337856</v>
+        <v>21.91536</v>
       </c>
       <c r="N58">
-        <v>18.17029603265306</v>
+        <v>14.38872163265306</v>
       </c>
       <c r="O58">
-        <v>4.542574008163264</v>
+        <v>3.597180408163265</v>
       </c>
       <c r="P58">
-        <v>13.62772202448979</v>
+        <v>10.79154122448979</v>
       </c>
       <c r="Q58">
-        <v>17.52772202448979</v>
+        <v>14.69154122448979</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.0963806253150625</v>
+        <v>0.09740646276736906</v>
       </c>
       <c r="T58">
-        <v>0.9859105330589585</v>
+        <v>1.005906014394659</v>
       </c>
       <c r="U58">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.002013392760806</v>
+        <v>1.656558762103523</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6208,22 +6208,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0803597789899687</v>
+        <v>0.0805120828413099</v>
       </c>
       <c r="C59">
-        <v>57.98203882476923</v>
+        <v>52.41478331222231</v>
       </c>
       <c r="D59">
-        <v>295.2060388247693</v>
+        <v>293.9107833122223</v>
       </c>
       <c r="E59">
-        <v>133.004</v>
+        <v>137.276</v>
       </c>
       <c r="F59">
-        <v>243.504</v>
+        <v>247.776</v>
       </c>
       <c r="G59">
         <v>6.28</v>
@@ -6244,28 +6244,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M59">
-        <v>21.91536</v>
+        <v>22.29984</v>
       </c>
       <c r="N59">
-        <v>14.38872163265306</v>
+        <v>14.00424163265306</v>
       </c>
       <c r="O59">
-        <v>3.597180408163265</v>
+        <v>3.501060408163265</v>
       </c>
       <c r="P59">
-        <v>10.79154122448979</v>
+        <v>10.50318122448979</v>
       </c>
       <c r="Q59">
-        <v>14.69154122448979</v>
+        <v>14.40318122448979</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09740646276736906</v>
+        <v>0.09848114962216642</v>
       </c>
       <c r="T59">
-        <v>1.005906014394659</v>
+        <v>1.026853661508251</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.656558762103523</v>
+        <v>1.627997404136221</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6290,22 +6290,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0805120828413099</v>
+        <v>0.08066438669265109</v>
       </c>
       <c r="C60">
-        <v>52.41478331222234</v>
+        <v>46.85884435629649</v>
       </c>
       <c r="D60">
-        <v>293.9107833122223</v>
+        <v>292.6268443562965</v>
       </c>
       <c r="E60">
-        <v>137.276</v>
+        <v>141.548</v>
       </c>
       <c r="F60">
-        <v>247.776</v>
+        <v>252.048</v>
       </c>
       <c r="G60">
         <v>6.28</v>
@@ -6326,28 +6326,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M60">
-        <v>22.29984</v>
+        <v>22.68432</v>
       </c>
       <c r="N60">
-        <v>14.00424163265306</v>
+        <v>13.61976163265306</v>
       </c>
       <c r="O60">
-        <v>3.501060408163266</v>
+        <v>3.404940408163266</v>
       </c>
       <c r="P60">
-        <v>10.5031812244898</v>
+        <v>10.2148212244898</v>
       </c>
       <c r="Q60">
-        <v>14.4031812244898</v>
+        <v>14.11482122448979</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09848114962216641</v>
+        <v>0.09960826022597827</v>
       </c>
       <c r="T60">
-        <v>1.026853661508251</v>
+        <v>1.048823145066408</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.627997404136221</v>
+        <v>1.600404227794929</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6372,22 +6372,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08066438669265109</v>
+        <v>0.08081669054399229</v>
       </c>
       <c r="C61">
-        <v>46.85884435629649</v>
+        <v>41.31407429410871</v>
       </c>
       <c r="D61">
-        <v>292.6268443562965</v>
+        <v>291.3540742941087</v>
       </c>
       <c r="E61">
-        <v>141.548</v>
+        <v>145.82</v>
       </c>
       <c r="F61">
-        <v>252.048</v>
+        <v>256.32</v>
       </c>
       <c r="G61">
         <v>6.28</v>
@@ -6408,28 +6408,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M61">
-        <v>22.68432</v>
+        <v>23.0688</v>
       </c>
       <c r="N61">
-        <v>13.61976163265306</v>
+        <v>13.23528163265306</v>
       </c>
       <c r="O61">
-        <v>3.404940408163266</v>
+        <v>3.308820408163265</v>
       </c>
       <c r="P61">
-        <v>10.2148212244898</v>
+        <v>9.926461224489795</v>
       </c>
       <c r="Q61">
-        <v>14.11482122448979</v>
+        <v>13.82646122448979</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09960826022597827</v>
+        <v>0.1007917263599807</v>
       </c>
       <c r="T61">
-        <v>1.048823145066408</v>
+        <v>1.071891102802472</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.600404227794929</v>
+        <v>1.573730823998347</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6454,22 +6454,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08081669054399229</v>
+        <v>0.0809689943953335</v>
       </c>
       <c r="C62">
-        <v>41.31407429410871</v>
+        <v>35.78032802066866</v>
       </c>
       <c r="D62">
-        <v>291.3540742941087</v>
+        <v>290.0923280206687</v>
       </c>
       <c r="E62">
-        <v>145.82</v>
+        <v>150.092</v>
       </c>
       <c r="F62">
-        <v>256.32</v>
+        <v>260.592</v>
       </c>
       <c r="G62">
         <v>6.28</v>
@@ -6490,28 +6490,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M62">
-        <v>23.0688</v>
+        <v>23.45328</v>
       </c>
       <c r="N62">
-        <v>13.23528163265306</v>
+        <v>12.85080163265306</v>
       </c>
       <c r="O62">
-        <v>3.308820408163265</v>
+        <v>3.212700408163265</v>
       </c>
       <c r="P62">
-        <v>9.926461224489795</v>
+        <v>9.638101224489795</v>
       </c>
       <c r="Q62">
-        <v>13.82646122448979</v>
+        <v>13.53810122448979</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1007917263599807</v>
+        <v>0.1020358830649577</v>
       </c>
       <c r="T62">
-        <v>1.071891102802472</v>
+        <v>1.09614203273013</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.573730823998347</v>
+        <v>1.547931958031161</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6536,22 +6536,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0809689943953335</v>
+        <v>0.08112129824667469</v>
       </c>
       <c r="C63">
-        <v>35.78032802066866</v>
+        <v>30.25746293373101</v>
       </c>
       <c r="D63">
-        <v>290.0923280206687</v>
+        <v>288.841462933731</v>
       </c>
       <c r="E63">
-        <v>150.092</v>
+        <v>154.364</v>
       </c>
       <c r="F63">
-        <v>260.592</v>
+        <v>264.864</v>
       </c>
       <c r="G63">
         <v>6.28</v>
@@ -6572,28 +6572,28 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M63">
-        <v>23.45328</v>
+        <v>23.83776</v>
       </c>
       <c r="N63">
-        <v>12.85080163265306</v>
+        <v>12.46632163265306</v>
       </c>
       <c r="O63">
-        <v>3.212700408163265</v>
+        <v>3.116580408163266</v>
       </c>
       <c r="P63">
-        <v>9.638101224489795</v>
+        <v>9.349741224489797</v>
       </c>
       <c r="Q63">
-        <v>13.53810122448979</v>
+        <v>13.2497412244898</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1020358830649577</v>
+        <v>0.1033455217017755</v>
       </c>
       <c r="T63">
-        <v>1.09614203273013</v>
+        <v>1.121669327390822</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.547931958031161</v>
+        <v>1.522965313546787</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6618,22 +6618,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08112129824667469</v>
+        <v>0.1103178798107484</v>
       </c>
       <c r="C64">
-        <v>30.25746293373101</v>
+        <v>-104.7253315990135</v>
       </c>
       <c r="D64">
-        <v>288.841462933731</v>
+        <v>158.1306684009865</v>
       </c>
       <c r="E64">
-        <v>154.364</v>
+        <v>158.636</v>
       </c>
       <c r="F64">
-        <v>264.864</v>
+        <v>269.136</v>
       </c>
       <c r="G64">
         <v>6.28</v>
@@ -6654,45 +6654,45 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M64">
-        <v>23.83776</v>
+        <v>39.5091648</v>
       </c>
       <c r="N64">
-        <v>12.46632163265306</v>
+        <v>-3.205083167346942</v>
       </c>
       <c r="O64">
-        <v>3.116580408163266</v>
+        <v>-0.8012707918367354</v>
       </c>
       <c r="P64">
-        <v>9.349741224489797</v>
+        <v>-2.403812375510206</v>
       </c>
       <c r="Q64">
-        <v>13.2497412244898</v>
+        <v>1.496187624489792</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1033455217017755</v>
+        <v>0.1056195836073676</v>
       </c>
       <c r="T64">
-        <v>1.121669327390822</v>
+        <v>1.165995026640012</v>
       </c>
       <c r="U64">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.25</v>
+        <v>0.2297193690149397</v>
       </c>
       <c r="W64">
-        <v>0.0675</v>
+        <v>0.1130771966286069</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>1.522965313546787</v>
+        <v>0.9188774760597587</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6700,22 +6700,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1103178798107484</v>
+        <v>0.1113278798107484</v>
       </c>
       <c r="C65">
-        <v>-104.7253315990135</v>
+        <v>-111.4346449310833</v>
       </c>
       <c r="D65">
-        <v>158.1306684009865</v>
+        <v>155.6933550689168</v>
       </c>
       <c r="E65">
-        <v>158.636</v>
+        <v>162.908</v>
       </c>
       <c r="F65">
-        <v>269.136</v>
+        <v>273.408</v>
       </c>
       <c r="G65">
         <v>6.28</v>
@@ -6736,37 +6736,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M65">
-        <v>39.5091648</v>
+        <v>40.1362944</v>
       </c>
       <c r="N65">
-        <v>-3.205083167346942</v>
+        <v>-3.832212767346945</v>
       </c>
       <c r="O65">
-        <v>-0.8012707918367354</v>
+        <v>-0.9580531918367363</v>
       </c>
       <c r="P65">
-        <v>-2.403812375510206</v>
+        <v>-2.874159575510209</v>
       </c>
       <c r="Q65">
-        <v>1.496187624489792</v>
+        <v>1.02584042448979</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1056195836073676</v>
+        <v>0.1072812387075723</v>
       </c>
       <c r="T65">
-        <v>1.165995026640012</v>
+        <v>1.198383777380013</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2297193690149397</v>
+        <v>0.2261300038740812</v>
       </c>
       <c r="W65">
-        <v>0.1130771966286069</v>
+        <v>0.1136041154312849</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.9188774760597587</v>
+        <v>0.9045200154963249</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6782,22 +6782,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1113278798107484</v>
+        <v>0.1123378798107484</v>
       </c>
       <c r="C66">
-        <v>-111.4346449310833</v>
+        <v>-118.0699647282706</v>
       </c>
       <c r="D66">
-        <v>155.6933550689168</v>
+        <v>153.3300352717294</v>
       </c>
       <c r="E66">
-        <v>162.908</v>
+        <v>167.18</v>
       </c>
       <c r="F66">
-        <v>273.408</v>
+        <v>277.68</v>
       </c>
       <c r="G66">
         <v>6.28</v>
@@ -6818,37 +6818,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M66">
-        <v>40.1362944</v>
+        <v>40.76342400000001</v>
       </c>
       <c r="N66">
-        <v>-3.832212767346945</v>
+        <v>-4.459342367346949</v>
       </c>
       <c r="O66">
-        <v>-0.9580531918367363</v>
+        <v>-1.114835591836737</v>
       </c>
       <c r="P66">
-        <v>-2.874159575510209</v>
+        <v>-3.344506775510212</v>
       </c>
       <c r="Q66">
-        <v>1.02584042448979</v>
+        <v>0.555493224489787</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1072812387075723</v>
+        <v>0.1090378455277887</v>
       </c>
       <c r="T66">
-        <v>1.198383777380013</v>
+        <v>1.232623313876585</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2261300038740812</v>
+        <v>0.2226510807375569</v>
       </c>
       <c r="W66">
-        <v>0.1136041154312849</v>
+        <v>0.1141148213477267</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.9045200154963249</v>
+        <v>0.8906043229502274</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6864,22 +6864,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1123378798107484</v>
+        <v>0.1133478798107484</v>
       </c>
       <c r="C67">
-        <v>-118.0699647282706</v>
+        <v>-124.6346101237786</v>
       </c>
       <c r="D67">
-        <v>153.3300352717294</v>
+        <v>151.0373898762214</v>
       </c>
       <c r="E67">
-        <v>167.18</v>
+        <v>171.452</v>
       </c>
       <c r="F67">
-        <v>277.68</v>
+        <v>281.952</v>
       </c>
       <c r="G67">
         <v>6.28</v>
@@ -6900,37 +6900,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M67">
-        <v>40.76342400000001</v>
+        <v>41.3905536</v>
       </c>
       <c r="N67">
-        <v>-4.459342367346949</v>
+        <v>-5.086471967346945</v>
       </c>
       <c r="O67">
-        <v>-1.114835591836737</v>
+        <v>-1.271617991836736</v>
       </c>
       <c r="P67">
-        <v>-3.344506775510212</v>
+        <v>-3.814853975510209</v>
       </c>
       <c r="Q67">
-        <v>0.555493224489787</v>
+        <v>0.0851460244897897</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1090378455277887</v>
+        <v>0.1108977821609589</v>
       </c>
       <c r="T67">
-        <v>1.232623313876585</v>
+        <v>1.268876940755308</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.2226510807375569</v>
+        <v>0.2192775795142606</v>
       </c>
       <c r="W67">
-        <v>0.1141148213477267</v>
+        <v>0.1146100513273066</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8906043229502274</v>
+        <v>0.8771103180570423</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6946,22 +6946,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1133478798107484</v>
+        <v>0.1143578798107484</v>
       </c>
       <c r="C68">
-        <v>-124.6346101237786</v>
+        <v>-131.1317046599003</v>
       </c>
       <c r="D68">
-        <v>151.0373898762214</v>
+        <v>148.8122953400997</v>
       </c>
       <c r="E68">
-        <v>171.452</v>
+        <v>175.724</v>
       </c>
       <c r="F68">
-        <v>281.952</v>
+        <v>286.224</v>
       </c>
       <c r="G68">
         <v>6.28</v>
@@ -6982,37 +6982,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M68">
-        <v>41.3905536</v>
+        <v>42.0176832</v>
       </c>
       <c r="N68">
-        <v>-5.086471967346945</v>
+        <v>-5.713601567346942</v>
       </c>
       <c r="O68">
-        <v>-1.271617991836736</v>
+        <v>-1.428400391836735</v>
       </c>
       <c r="P68">
-        <v>-3.814853975510209</v>
+        <v>-4.285201175510206</v>
       </c>
       <c r="Q68">
-        <v>0.0851460244897897</v>
+        <v>-0.3852011755102076</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1108977821609589</v>
+        <v>0.1128704422264425</v>
       </c>
       <c r="T68">
-        <v>1.268876940755308</v>
+        <v>1.307327757141832</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.2192775795142606</v>
+        <v>0.2160047798200179</v>
       </c>
       <c r="W68">
-        <v>0.1146100513273066</v>
+        <v>0.1150904983224214</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8771103180570423</v>
+        <v>0.8640191192800716</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7028,22 +7028,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1143578798107484</v>
+        <v>0.1153678798107484</v>
       </c>
       <c r="C69">
-        <v>-131.1317046599003</v>
+        <v>-137.564190486152</v>
       </c>
       <c r="D69">
-        <v>148.8122953400997</v>
+        <v>146.6518095138481</v>
       </c>
       <c r="E69">
-        <v>175.724</v>
+        <v>179.996</v>
       </c>
       <c r="F69">
-        <v>286.224</v>
+        <v>290.496</v>
       </c>
       <c r="G69">
         <v>6.28</v>
@@ -7064,37 +7064,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M69">
-        <v>42.0176832</v>
+        <v>42.64481280000001</v>
       </c>
       <c r="N69">
-        <v>-5.713601567346942</v>
+        <v>-6.340731167346952</v>
       </c>
       <c r="O69">
-        <v>-1.428400391836735</v>
+        <v>-1.585182791836738</v>
       </c>
       <c r="P69">
-        <v>-4.285201175510206</v>
+        <v>-4.755548375510214</v>
       </c>
       <c r="Q69">
-        <v>-0.3852011755102076</v>
+        <v>-0.8555483755102156</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1128704422264425</v>
+        <v>0.1149663935460189</v>
       </c>
       <c r="T69">
-        <v>1.307327757141832</v>
+        <v>1.348181749552515</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2160047798200179</v>
+        <v>0.2128282389403117</v>
       </c>
       <c r="W69">
-        <v>0.1150904983224214</v>
+        <v>0.1155568145235623</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8640191192800716</v>
+        <v>0.8513129557612468</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7110,22 +7110,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1153678798107484</v>
+        <v>0.1163778798107484</v>
       </c>
       <c r="C70">
-        <v>-137.564190486152</v>
+        <v>-143.9348413383192</v>
       </c>
       <c r="D70">
-        <v>146.6518095138481</v>
+        <v>144.5531586616808</v>
       </c>
       <c r="E70">
-        <v>179.996</v>
+        <v>184.268</v>
       </c>
       <c r="F70">
-        <v>290.496</v>
+        <v>294.768</v>
       </c>
       <c r="G70">
         <v>6.28</v>
@@ -7146,37 +7146,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M70">
-        <v>42.64481280000001</v>
+        <v>43.27194240000001</v>
       </c>
       <c r="N70">
-        <v>-6.340731167346952</v>
+        <v>-6.967860767346949</v>
       </c>
       <c r="O70">
-        <v>-1.585182791836738</v>
+        <v>-1.741965191836737</v>
       </c>
       <c r="P70">
-        <v>-4.755548375510214</v>
+        <v>-5.225895575510211</v>
       </c>
       <c r="Q70">
-        <v>-0.8555483755102156</v>
+        <v>-1.325895575510213</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1149663935460189</v>
+        <v>0.1171975675313743</v>
       </c>
       <c r="T70">
-        <v>1.348181749552515</v>
+        <v>1.391671483409048</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2128282389403117</v>
+        <v>0.2097437717092927</v>
       </c>
       <c r="W70">
-        <v>0.1155568145235623</v>
+        <v>0.1160096143130758</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8513129557612468</v>
+        <v>0.8389750868371708</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7192,22 +7192,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1163778798107484</v>
+        <v>0.1173878798107484</v>
       </c>
       <c r="C71">
-        <v>-143.9348413383192</v>
+        <v>-150.2462744188108</v>
       </c>
       <c r="D71">
-        <v>144.5531586616808</v>
+        <v>142.5137255811892</v>
       </c>
       <c r="E71">
-        <v>184.268</v>
+        <v>188.54</v>
       </c>
       <c r="F71">
-        <v>294.768</v>
+        <v>299.04</v>
       </c>
       <c r="G71">
         <v>6.28</v>
@@ -7228,37 +7228,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M71">
-        <v>43.27194240000001</v>
+        <v>43.899072</v>
       </c>
       <c r="N71">
-        <v>-6.967860767346949</v>
+        <v>-7.594990367346945</v>
       </c>
       <c r="O71">
-        <v>-1.741965191836737</v>
+        <v>-1.898747591836736</v>
       </c>
       <c r="P71">
-        <v>-5.225895575510211</v>
+        <v>-5.696242775510209</v>
       </c>
       <c r="Q71">
-        <v>-1.325895575510213</v>
+        <v>-1.79624277551021</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1171975675313743</v>
+        <v>0.1195774864490868</v>
       </c>
       <c r="T71">
-        <v>1.391671483409048</v>
+        <v>1.438060532856016</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.2097437717092927</v>
+        <v>0.2067474321134457</v>
       </c>
       <c r="W71">
-        <v>0.1160096143130758</v>
+        <v>0.1164494769657462</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8389750868371708</v>
+        <v>0.8269897284537827</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7274,22 +7274,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1173878798107484</v>
+        <v>0.1183978798107484</v>
       </c>
       <c r="C72">
-        <v>-150.2462744188108</v>
+        <v>-156.5009612853175</v>
       </c>
       <c r="D72">
-        <v>142.5137255811892</v>
+        <v>140.5310387146825</v>
       </c>
       <c r="E72">
-        <v>188.54</v>
+        <v>192.812</v>
       </c>
       <c r="F72">
-        <v>299.04</v>
+        <v>303.312</v>
       </c>
       <c r="G72">
         <v>6.28</v>
@@ -7310,37 +7310,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M72">
-        <v>43.899072</v>
+        <v>44.52620160000001</v>
       </c>
       <c r="N72">
-        <v>-7.594990367346945</v>
+        <v>-8.222119967346948</v>
       </c>
       <c r="O72">
-        <v>-1.898747591836736</v>
+        <v>-2.055529991836737</v>
       </c>
       <c r="P72">
-        <v>-5.696242775510209</v>
+        <v>-6.166589975510211</v>
       </c>
       <c r="Q72">
-        <v>-1.79624277551021</v>
+        <v>-2.266589975510213</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1195774864490868</v>
+        <v>0.1221215377059519</v>
       </c>
       <c r="T72">
-        <v>1.438060532856016</v>
+        <v>1.48764882709243</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2067474321134457</v>
+        <v>0.203835496449876</v>
       </c>
       <c r="W72">
-        <v>0.1164494769657462</v>
+        <v>0.1168769491211582</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8269897284537827</v>
+        <v>0.815341985799504</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7356,22 +7356,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1183978798107484</v>
+        <v>0.1194078798107484</v>
       </c>
       <c r="C73">
-        <v>-156.5009612853175</v>
+        <v>-162.7012378430279</v>
       </c>
       <c r="D73">
-        <v>140.5310387146825</v>
+        <v>138.6027621569721</v>
       </c>
       <c r="E73">
-        <v>192.812</v>
+        <v>197.084</v>
       </c>
       <c r="F73">
-        <v>303.312</v>
+        <v>307.584</v>
       </c>
       <c r="G73">
         <v>6.28</v>
@@ -7392,37 +7392,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M73">
-        <v>44.5262016</v>
+        <v>45.1533312</v>
       </c>
       <c r="N73">
-        <v>-8.222119967346941</v>
+        <v>-8.849249567346945</v>
       </c>
       <c r="O73">
-        <v>-2.055529991836735</v>
+        <v>-2.212312391836736</v>
       </c>
       <c r="P73">
-        <v>-6.166589975510206</v>
+        <v>-6.636937175510209</v>
       </c>
       <c r="Q73">
-        <v>-2.266589975510207</v>
+        <v>-2.73693717551021</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1221215377059518</v>
+        <v>0.1248473069097358</v>
       </c>
       <c r="T73">
-        <v>1.48764882709243</v>
+        <v>1.540779142345731</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.203835496449876</v>
+        <v>0.2010044478880722</v>
       </c>
       <c r="W73">
-        <v>0.1168769491211582</v>
+        <v>0.117292547050031</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8153419857995041</v>
+        <v>0.8040177915522888</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7438,22 +7438,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1194078798107484</v>
+        <v>0.1608450587477747</v>
       </c>
       <c r="C74">
-        <v>-162.7012378430279</v>
+        <v>-216.895481520231</v>
       </c>
       <c r="D74">
-        <v>138.6027621569721</v>
+        <v>88.68051847976895</v>
       </c>
       <c r="E74">
-        <v>197.084</v>
+        <v>201.356</v>
       </c>
       <c r="F74">
-        <v>307.584</v>
+        <v>311.856</v>
       </c>
       <c r="G74">
         <v>6.28</v>
@@ -7474,45 +7474,45 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M74">
-        <v>45.1533312</v>
+        <v>62.6206848</v>
       </c>
       <c r="N74">
-        <v>-8.849249567346945</v>
+        <v>-26.31660316734694</v>
       </c>
       <c r="O74">
-        <v>-2.212312391836736</v>
+        <v>-6.579150791836735</v>
       </c>
       <c r="P74">
-        <v>-6.636937175510209</v>
+        <v>-19.73745237551021</v>
       </c>
       <c r="Q74">
-        <v>-2.73693717551021</v>
+        <v>-15.83745237551021</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1248473069097358</v>
+        <v>0.1315052773027866</v>
       </c>
       <c r="T74">
-        <v>1.540779142345731</v>
+        <v>1.670555377780067</v>
       </c>
       <c r="U74">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.2010044478880722</v>
+        <v>0.1449364604866676</v>
       </c>
       <c r="W74">
-        <v>0.117292547050031</v>
+        <v>0.1716967587342771</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.8040177915522888</v>
+        <v>0.5797458419466703</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7520,22 +7520,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1608450587477747</v>
+        <v>0.1623950587477747</v>
       </c>
       <c r="C75">
-        <v>-216.895481520231</v>
+        <v>-222.3463891439322</v>
       </c>
       <c r="D75">
-        <v>88.68051847976895</v>
+        <v>87.50161085606777</v>
       </c>
       <c r="E75">
-        <v>201.356</v>
+        <v>205.628</v>
       </c>
       <c r="F75">
-        <v>311.856</v>
+        <v>316.128</v>
       </c>
       <c r="G75">
         <v>6.28</v>
@@ -7556,37 +7556,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M75">
-        <v>62.6206848</v>
+        <v>63.4785024</v>
       </c>
       <c r="N75">
-        <v>-26.31660316734694</v>
+        <v>-27.17442076734694</v>
       </c>
       <c r="O75">
-        <v>-6.579150791836735</v>
+        <v>-6.793605191836734</v>
       </c>
       <c r="P75">
-        <v>-19.73745237551021</v>
+        <v>-20.3808155755102</v>
       </c>
       <c r="Q75">
-        <v>-15.83745237551021</v>
+        <v>-16.48081557551021</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1315052773027866</v>
+        <v>0.1348016341221246</v>
       </c>
       <c r="T75">
-        <v>1.670555377780067</v>
+        <v>1.734807507694685</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1449364604866676</v>
+        <v>0.1429778596692802</v>
       </c>
       <c r="W75">
-        <v>0.1716967587342771</v>
+        <v>0.1720900457784086</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5797458419466703</v>
+        <v>0.5719114386771207</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7602,22 +7602,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1623950587477747</v>
+        <v>0.1639450587477747</v>
       </c>
       <c r="C76">
-        <v>-222.3463891439322</v>
+        <v>-227.7663634922835</v>
       </c>
       <c r="D76">
-        <v>87.50161085606777</v>
+        <v>86.35363650771643</v>
       </c>
       <c r="E76">
-        <v>205.628</v>
+        <v>209.9</v>
       </c>
       <c r="F76">
-        <v>316.128</v>
+        <v>320.4</v>
       </c>
       <c r="G76">
         <v>6.28</v>
@@ -7638,37 +7638,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M76">
-        <v>63.4785024</v>
+        <v>64.33632</v>
       </c>
       <c r="N76">
-        <v>-27.17442076734694</v>
+        <v>-28.03223836734694</v>
       </c>
       <c r="O76">
-        <v>-6.793605191836734</v>
+        <v>-7.008059591836735</v>
       </c>
       <c r="P76">
-        <v>-20.3808155755102</v>
+        <v>-21.02417877551021</v>
       </c>
       <c r="Q76">
-        <v>-16.48081557551021</v>
+        <v>-17.12417877551021</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1348016341221246</v>
+        <v>0.1383616994870096</v>
       </c>
       <c r="T76">
-        <v>1.734807507694685</v>
+        <v>1.804199808002472</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1429778596692802</v>
+        <v>0.1410714882070231</v>
       </c>
       <c r="W76">
-        <v>0.1720900457784086</v>
+        <v>0.1724728451680298</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5719114386771207</v>
+        <v>0.5642859528280924</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7684,22 +7684,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1639450587477747</v>
+        <v>0.1654950587477747</v>
       </c>
       <c r="C77">
-        <v>-227.7663634922835</v>
+        <v>-233.1566062834835</v>
       </c>
       <c r="D77">
-        <v>86.35363650771643</v>
+        <v>85.23539371651646</v>
       </c>
       <c r="E77">
-        <v>209.9</v>
+        <v>214.172</v>
       </c>
       <c r="F77">
-        <v>320.4</v>
+        <v>324.672</v>
       </c>
       <c r="G77">
         <v>6.28</v>
@@ -7720,37 +7720,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M77">
-        <v>64.33632</v>
+        <v>65.19413759999999</v>
       </c>
       <c r="N77">
-        <v>-28.03223836734694</v>
+        <v>-28.89005596734693</v>
       </c>
       <c r="O77">
-        <v>-7.008059591836735</v>
+        <v>-7.222513991836733</v>
       </c>
       <c r="P77">
-        <v>-21.02417877551021</v>
+        <v>-21.6675419755102</v>
       </c>
       <c r="Q77">
-        <v>-17.12417877551021</v>
+        <v>-17.7675419755102</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1383616994870096</v>
+        <v>0.142218436965635</v>
       </c>
       <c r="T77">
-        <v>1.804199808002472</v>
+        <v>1.879374800002575</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1410714882070231</v>
+        <v>0.1392152844148254</v>
       </c>
       <c r="W77">
-        <v>0.1724728451680298</v>
+        <v>0.1728455708895031</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5642859528280924</v>
+        <v>0.5568611376593018</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7766,22 +7766,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1654950587477747</v>
+        <v>0.1670450587477747</v>
       </c>
       <c r="C78">
-        <v>-233.1566062834835</v>
+        <v>-238.5182577845434</v>
       </c>
       <c r="D78">
-        <v>85.23539371651646</v>
+        <v>84.14574221545661</v>
       </c>
       <c r="E78">
-        <v>214.172</v>
+        <v>218.444</v>
       </c>
       <c r="F78">
-        <v>324.672</v>
+        <v>328.944</v>
       </c>
       <c r="G78">
         <v>6.28</v>
@@ -7802,37 +7802,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M78">
-        <v>65.19413759999999</v>
+        <v>66.05195520000001</v>
       </c>
       <c r="N78">
-        <v>-28.89005596734693</v>
+        <v>-29.74787356734695</v>
       </c>
       <c r="O78">
-        <v>-7.222513991836733</v>
+        <v>-7.436968391836738</v>
       </c>
       <c r="P78">
-        <v>-21.6675419755102</v>
+        <v>-22.31090517551021</v>
       </c>
       <c r="Q78">
-        <v>-17.7675419755102</v>
+        <v>-18.41090517551022</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.142218436965635</v>
+        <v>0.1464105429206626</v>
       </c>
       <c r="T78">
-        <v>1.879374800002575</v>
+        <v>1.961086747828774</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1392152844148254</v>
+        <v>0.1374072937081394</v>
       </c>
       <c r="W78">
-        <v>0.1728455708895031</v>
+        <v>0.1732086154234056</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5568611376593018</v>
+        <v>0.5496291748325575</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7848,22 +7848,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1670450587477747</v>
+        <v>0.1685950587477747</v>
       </c>
       <c r="C79">
-        <v>-238.5182577845434</v>
+        <v>-243.8524006896733</v>
       </c>
       <c r="D79">
-        <v>84.14574221545661</v>
+        <v>83.08359931032672</v>
       </c>
       <c r="E79">
-        <v>218.444</v>
+        <v>222.716</v>
       </c>
       <c r="F79">
-        <v>328.944</v>
+        <v>333.216</v>
       </c>
       <c r="G79">
         <v>6.28</v>
@@ -7884,37 +7884,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M79">
-        <v>66.05195520000001</v>
+        <v>66.9097728</v>
       </c>
       <c r="N79">
-        <v>-29.74787356734695</v>
+        <v>-30.60569116734694</v>
       </c>
       <c r="O79">
-        <v>-7.436968391836738</v>
+        <v>-7.651422791836735</v>
       </c>
       <c r="P79">
-        <v>-22.31090517551021</v>
+        <v>-22.9542683755102</v>
       </c>
       <c r="Q79">
-        <v>-18.41090517551022</v>
+        <v>-19.0542683755102</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1464105429206626</v>
+        <v>0.1509837494170564</v>
       </c>
       <c r="T79">
-        <v>1.961086747828774</v>
+        <v>2.050227054548264</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1374072937081394</v>
+        <v>0.1356456617375222</v>
       </c>
       <c r="W79">
-        <v>0.1732086154234056</v>
+        <v>0.1735623511231055</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5496291748325575</v>
+        <v>0.542582646950089</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7930,22 +7930,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1685950587477747</v>
+        <v>0.1701450587477747</v>
       </c>
       <c r="C80">
-        <v>-243.8524006896733</v>
+        <v>-249.1600637085974</v>
       </c>
       <c r="D80">
-        <v>83.08359931032672</v>
+        <v>82.04793629140265</v>
       </c>
       <c r="E80">
-        <v>222.716</v>
+        <v>226.988</v>
       </c>
       <c r="F80">
-        <v>333.216</v>
+        <v>337.488</v>
       </c>
       <c r="G80">
         <v>6.28</v>
@@ -7966,37 +7966,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M80">
-        <v>66.9097728</v>
+        <v>67.7675904</v>
       </c>
       <c r="N80">
-        <v>-30.60569116734694</v>
+        <v>-31.46350876734694</v>
       </c>
       <c r="O80">
-        <v>-7.651422791836735</v>
+        <v>-7.865877191836736</v>
       </c>
       <c r="P80">
-        <v>-22.9542683755102</v>
+        <v>-23.59763157551021</v>
       </c>
       <c r="Q80">
-        <v>-19.0542683755102</v>
+        <v>-19.69763157551021</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1509837494170564</v>
+        <v>0.1559924993892972</v>
       </c>
       <c r="T80">
-        <v>2.050227054548264</v>
+        <v>2.147856914288658</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1356456617375222</v>
+        <v>0.1339286280446422</v>
       </c>
       <c r="W80">
-        <v>0.1735623511231055</v>
+        <v>0.1739071314886359</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.542582646950089</v>
+        <v>0.5357145121785687</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8012,22 +8012,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1701450587477747</v>
+        <v>0.1716950587477747</v>
       </c>
       <c r="C81">
-        <v>-249.1600637085974</v>
+        <v>-254.4422248897955</v>
       </c>
       <c r="D81">
-        <v>82.04793629140265</v>
+        <v>81.03777511020445</v>
       </c>
       <c r="E81">
-        <v>226.988</v>
+        <v>231.26</v>
       </c>
       <c r="F81">
-        <v>337.488</v>
+        <v>341.76</v>
       </c>
       <c r="G81">
         <v>6.28</v>
@@ -8048,37 +8048,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M81">
-        <v>67.7675904</v>
+        <v>68.62540800000001</v>
       </c>
       <c r="N81">
-        <v>-31.46350876734694</v>
+        <v>-32.32132636734695</v>
       </c>
       <c r="O81">
-        <v>-7.865877191836736</v>
+        <v>-8.080331591836737</v>
       </c>
       <c r="P81">
-        <v>-23.59763157551021</v>
+        <v>-24.24099477551021</v>
       </c>
       <c r="Q81">
-        <v>-19.69763157551021</v>
+        <v>-20.34099477551021</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1559924993892972</v>
+        <v>0.161502124358762</v>
       </c>
       <c r="T81">
-        <v>2.147856914288658</v>
+        <v>2.255249760003091</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1339286280446422</v>
+        <v>0.1322545201940842</v>
       </c>
       <c r="W81">
-        <v>0.1739071314886359</v>
+        <v>0.1742432923450279</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5357145121785687</v>
+        <v>0.5290180807763366</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8094,22 +8094,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1716950587477747</v>
+        <v>0.1732450587477747</v>
       </c>
       <c r="C82">
-        <v>-254.4422248897955</v>
+        <v>-259.6998147012406</v>
       </c>
       <c r="D82">
-        <v>81.03777511020445</v>
+        <v>80.05218529875941</v>
       </c>
       <c r="E82">
-        <v>231.26</v>
+        <v>235.532</v>
       </c>
       <c r="F82">
-        <v>341.76</v>
+        <v>346.032</v>
       </c>
       <c r="G82">
         <v>6.28</v>
@@ -8130,37 +8130,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M82">
-        <v>68.62540800000001</v>
+        <v>69.48322560000001</v>
       </c>
       <c r="N82">
-        <v>-32.32132636734695</v>
+        <v>-33.17914396734695</v>
       </c>
       <c r="O82">
-        <v>-8.080331591836737</v>
+        <v>-8.294785991836738</v>
       </c>
       <c r="P82">
-        <v>-24.24099477551021</v>
+        <v>-24.88435797551021</v>
       </c>
       <c r="Q82">
-        <v>-20.34099477551021</v>
+        <v>-20.98435797551021</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.161502124358762</v>
+        <v>0.1675917098513284</v>
       </c>
       <c r="T82">
-        <v>2.255249760003091</v>
+        <v>2.373947115792727</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1322545201940842</v>
+        <v>0.1306217483398362</v>
       </c>
       <c r="W82">
-        <v>0.1742432923450279</v>
+        <v>0.1745711529333609</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5290180807763366</v>
+        <v>0.5224869933593448</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8176,22 +8176,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1732450587477747</v>
+        <v>0.1747950587477747</v>
       </c>
       <c r="C83">
-        <v>-259.6998147012406</v>
+        <v>-264.9337188890258</v>
       </c>
       <c r="D83">
-        <v>80.05218529875941</v>
+        <v>79.09028111097425</v>
       </c>
       <c r="E83">
-        <v>235.532</v>
+        <v>239.804</v>
       </c>
       <c r="F83">
-        <v>346.032</v>
+        <v>350.304</v>
       </c>
       <c r="G83">
         <v>6.28</v>
@@ -8212,37 +8212,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M83">
-        <v>69.48322560000001</v>
+        <v>70.3410432</v>
       </c>
       <c r="N83">
-        <v>-33.17914396734695</v>
+        <v>-34.03696156734694</v>
       </c>
       <c r="O83">
-        <v>-8.294785991836738</v>
+        <v>-8.509240391836736</v>
       </c>
       <c r="P83">
-        <v>-24.88435797551021</v>
+        <v>-25.52772117551021</v>
       </c>
       <c r="Q83">
-        <v>-20.98435797551021</v>
+        <v>-21.62772117551021</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1675917098513284</v>
+        <v>0.17435791595418</v>
       </c>
       <c r="T83">
-        <v>2.373947115792727</v>
+        <v>2.505833066670101</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1306217483398362</v>
+        <v>0.1290288001893504</v>
       </c>
       <c r="W83">
-        <v>0.1745711529333609</v>
+        <v>0.1748910169219784</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5224869933593448</v>
+        <v>0.5161152007574016</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8258,22 +8258,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1747950587477747</v>
+        <v>0.1763450587477748</v>
       </c>
       <c r="C84">
-        <v>-264.9337188890258</v>
+        <v>-270.1447811323457</v>
       </c>
       <c r="D84">
-        <v>79.09028111097425</v>
+        <v>78.15121886765438</v>
       </c>
       <c r="E84">
-        <v>239.804</v>
+        <v>244.076</v>
       </c>
       <c r="F84">
-        <v>350.304</v>
+        <v>354.576</v>
       </c>
       <c r="G84">
         <v>6.28</v>
@@ -8294,37 +8294,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M84">
-        <v>70.3410432</v>
+        <v>71.19886080000001</v>
       </c>
       <c r="N84">
-        <v>-34.03696156734694</v>
+        <v>-34.89477916734695</v>
       </c>
       <c r="O84">
-        <v>-8.509240391836736</v>
+        <v>-8.723694791836737</v>
       </c>
       <c r="P84">
-        <v>-25.52772117551021</v>
+        <v>-26.17108437551021</v>
       </c>
       <c r="Q84">
-        <v>-21.62772117551021</v>
+        <v>-22.27108437551021</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.17435791595418</v>
+        <v>0.1819201463044259</v>
       </c>
       <c r="T84">
-        <v>2.505833066670101</v>
+        <v>2.653235011768343</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1290288001893504</v>
+        <v>0.1274742363316474</v>
       </c>
       <c r="W84">
-        <v>0.1748910169219784</v>
+        <v>0.1752031733446052</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5161152007574016</v>
+        <v>0.5098969453265895</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8340,22 +8340,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1763450587477748</v>
+        <v>0.1778950587477747</v>
       </c>
       <c r="C85">
-        <v>-270.1447811323457</v>
+        <v>-275.3338055115555</v>
       </c>
       <c r="D85">
-        <v>78.15121886765438</v>
+        <v>77.23419448844454</v>
       </c>
       <c r="E85">
-        <v>244.076</v>
+        <v>248.348</v>
       </c>
       <c r="F85">
-        <v>354.576</v>
+        <v>358.848</v>
       </c>
       <c r="G85">
         <v>6.28</v>
@@ -8376,37 +8376,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M85">
-        <v>71.19886080000001</v>
+        <v>72.05667840000001</v>
       </c>
       <c r="N85">
-        <v>-34.89477916734695</v>
+        <v>-35.75259676734695</v>
       </c>
       <c r="O85">
-        <v>-8.723694791836737</v>
+        <v>-8.938149191836738</v>
       </c>
       <c r="P85">
-        <v>-26.17108437551021</v>
+        <v>-26.81444757551021</v>
       </c>
       <c r="Q85">
-        <v>-22.27108437551021</v>
+        <v>-22.91444757551022</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1819201463044259</v>
+        <v>0.1904276554484526</v>
       </c>
       <c r="T85">
-        <v>2.653235011768343</v>
+        <v>2.819062200003864</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1274742363316474</v>
+        <v>0.1259566858991278</v>
       </c>
       <c r="W85">
-        <v>0.1752031733446052</v>
+        <v>0.1755078974714551</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5098969453265895</v>
+        <v>0.503826743596511</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8422,22 +8422,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1778950587477747</v>
+        <v>0.2096014676142373</v>
       </c>
       <c r="C86">
-        <v>-275.3338055115554</v>
+        <v>-294.5557261965741</v>
       </c>
       <c r="D86">
-        <v>77.23419448844459</v>
+        <v>62.28427380342586</v>
       </c>
       <c r="E86">
-        <v>248.348</v>
+        <v>252.62</v>
       </c>
       <c r="F86">
-        <v>358.848</v>
+        <v>363.12</v>
       </c>
       <c r="G86">
         <v>6.28</v>
@@ -8458,45 +8458,45 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M86">
-        <v>72.0566784</v>
+        <v>85.62369600000001</v>
       </c>
       <c r="N86">
-        <v>-35.75259676734694</v>
+        <v>-49.31961436734695</v>
       </c>
       <c r="O86">
-        <v>-8.938149191836734</v>
+        <v>-12.32990359183674</v>
       </c>
       <c r="P86">
-        <v>-26.8144475755102</v>
+        <v>-36.98971077551021</v>
       </c>
       <c r="Q86">
-        <v>-22.9144475755102</v>
+        <v>-33.08971077551021</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1904276554484524</v>
+        <v>0.2027788915880999</v>
       </c>
       <c r="T86">
-        <v>2.819062200003863</v>
+        <v>3.059810781709328</v>
       </c>
       <c r="U86">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1259566858991278</v>
+        <v>0.105998932914123</v>
       </c>
       <c r="W86">
-        <v>0.1755078974714551</v>
+        <v>0.2108054516188498</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.5038267435965111</v>
+        <v>0.4239957316564921</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8504,22 +8504,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2096014676142373</v>
+        <v>0.2115014676142373</v>
       </c>
       <c r="C87">
-        <v>-294.5557261965741</v>
+        <v>-299.5419028537298</v>
       </c>
       <c r="D87">
-        <v>62.28427380342586</v>
+        <v>61.57009714627021</v>
       </c>
       <c r="E87">
-        <v>252.62</v>
+        <v>256.892</v>
       </c>
       <c r="F87">
-        <v>363.12</v>
+        <v>367.392</v>
       </c>
       <c r="G87">
         <v>6.28</v>
@@ -8540,37 +8540,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M87">
-        <v>85.62369600000001</v>
+        <v>86.63103360000001</v>
       </c>
       <c r="N87">
-        <v>-49.31961436734695</v>
+        <v>-50.32695196734695</v>
       </c>
       <c r="O87">
-        <v>-12.32990359183674</v>
+        <v>-12.58173799183674</v>
       </c>
       <c r="P87">
-        <v>-36.98971077551021</v>
+        <v>-37.74521397551021</v>
       </c>
       <c r="Q87">
-        <v>-33.08971077551021</v>
+        <v>-33.84521397551021</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2027788915880999</v>
+        <v>0.2139916695586784</v>
       </c>
       <c r="T87">
-        <v>3.059810781709328</v>
+        <v>3.278368694688566</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.105998932914123</v>
+        <v>0.1047663871825635</v>
       </c>
       <c r="W87">
-        <v>0.2108054516188498</v>
+        <v>0.2110960859023515</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4239957316564921</v>
+        <v>0.4190655487302538</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8586,22 +8586,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2115014676142373</v>
+        <v>0.2134014676142373</v>
       </c>
       <c r="C88">
-        <v>-299.5419028537298</v>
+        <v>-304.5118871031706</v>
       </c>
       <c r="D88">
-        <v>61.57009714627021</v>
+        <v>60.87211289682939</v>
       </c>
       <c r="E88">
-        <v>256.892</v>
+        <v>261.164</v>
       </c>
       <c r="F88">
-        <v>367.392</v>
+        <v>371.664</v>
       </c>
       <c r="G88">
         <v>6.28</v>
@@ -8622,37 +8622,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M88">
-        <v>86.63103360000001</v>
+        <v>87.63837119999999</v>
       </c>
       <c r="N88">
-        <v>-50.32695196734695</v>
+        <v>-51.33428956734694</v>
       </c>
       <c r="O88">
-        <v>-12.58173799183674</v>
+        <v>-12.83357239183673</v>
       </c>
       <c r="P88">
-        <v>-37.74521397551021</v>
+        <v>-38.5007171755102</v>
       </c>
       <c r="Q88">
-        <v>-33.84521397551021</v>
+        <v>-34.6007171755102</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2139916695586784</v>
+        <v>0.2269294902939614</v>
       </c>
       <c r="T88">
-        <v>3.278368694688566</v>
+        <v>3.530550901972302</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1047663871825635</v>
+        <v>0.1035621758356375</v>
       </c>
       <c r="W88">
-        <v>0.2110960859023515</v>
+        <v>0.2113800389379567</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4190655487302538</v>
+        <v>0.4142487033425498</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8668,22 +8668,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2134014676142373</v>
+        <v>0.2153014676142373</v>
       </c>
       <c r="C89">
-        <v>-304.5118871031706</v>
+        <v>-309.4662234636273</v>
       </c>
       <c r="D89">
-        <v>60.87211289682939</v>
+        <v>60.18977653637265</v>
       </c>
       <c r="E89">
-        <v>261.164</v>
+        <v>265.436</v>
       </c>
       <c r="F89">
-        <v>371.664</v>
+        <v>375.936</v>
       </c>
       <c r="G89">
         <v>6.28</v>
@@ -8704,37 +8704,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M89">
-        <v>87.63837119999999</v>
+        <v>88.64570879999999</v>
       </c>
       <c r="N89">
-        <v>-51.33428956734694</v>
+        <v>-52.34162716734694</v>
       </c>
       <c r="O89">
-        <v>-12.83357239183673</v>
+        <v>-13.08540679183673</v>
       </c>
       <c r="P89">
-        <v>-38.5007171755102</v>
+        <v>-39.2562203755102</v>
       </c>
       <c r="Q89">
-        <v>-34.6007171755102</v>
+        <v>-35.3562203755102</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2269294902939614</v>
+        <v>0.2420236144851249</v>
       </c>
       <c r="T89">
-        <v>3.530550901972302</v>
+        <v>3.82476347713666</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1035621758356375</v>
+        <v>0.1023853329284143</v>
       </c>
       <c r="W89">
-        <v>0.2113800389379567</v>
+        <v>0.2116575384954799</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4142487033425498</v>
+        <v>0.4095413317136573</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8750,22 +8750,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2153014676142373</v>
+        <v>0.2172014676142373</v>
       </c>
       <c r="C90">
-        <v>-309.4662234636273</v>
+        <v>-314.4054323096828</v>
       </c>
       <c r="D90">
-        <v>60.18977653637265</v>
+        <v>59.52256769031717</v>
       </c>
       <c r="E90">
-        <v>265.436</v>
+        <v>269.708</v>
       </c>
       <c r="F90">
-        <v>375.936</v>
+        <v>380.208</v>
       </c>
       <c r="G90">
         <v>6.28</v>
@@ -8786,37 +8786,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M90">
-        <v>88.64570879999999</v>
+        <v>89.65304639999999</v>
       </c>
       <c r="N90">
-        <v>-52.34162716734694</v>
+        <v>-53.34896476734693</v>
       </c>
       <c r="O90">
-        <v>-13.08540679183673</v>
+        <v>-13.33724119183673</v>
       </c>
       <c r="P90">
-        <v>-39.2562203755102</v>
+        <v>-40.0117235755102</v>
       </c>
       <c r="Q90">
-        <v>-35.3562203755102</v>
+        <v>-36.1117235755102</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2420236144851249</v>
+        <v>0.2598621248928635</v>
       </c>
       <c r="T90">
-        <v>3.82476347713666</v>
+        <v>4.172469247785448</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1023853329284143</v>
+        <v>0.1012349359292186</v>
       </c>
       <c r="W90">
-        <v>0.2116575384954799</v>
+        <v>0.2119288021078903</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4095413317136573</v>
+        <v>0.4049397437168746</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8832,22 +8832,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2172014676142373</v>
+        <v>0.2191014676142373</v>
       </c>
       <c r="C91">
-        <v>-314.4054323096828</v>
+        <v>-319.3300111953005</v>
       </c>
       <c r="D91">
-        <v>59.52256769031717</v>
+        <v>58.86998880469948</v>
       </c>
       <c r="E91">
-        <v>269.708</v>
+        <v>273.98</v>
       </c>
       <c r="F91">
-        <v>380.208</v>
+        <v>384.48</v>
       </c>
       <c r="G91">
         <v>6.28</v>
@@ -8868,37 +8868,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M91">
-        <v>89.65304639999999</v>
+        <v>90.66038400000001</v>
       </c>
       <c r="N91">
-        <v>-53.34896476734693</v>
+        <v>-54.35630236734695</v>
       </c>
       <c r="O91">
-        <v>-13.33724119183673</v>
+        <v>-13.58907559183674</v>
       </c>
       <c r="P91">
-        <v>-40.0117235755102</v>
+        <v>-40.76722677551021</v>
       </c>
       <c r="Q91">
-        <v>-36.1117235755102</v>
+        <v>-36.86722677551021</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2598621248928635</v>
+        <v>0.2812683373821498</v>
       </c>
       <c r="T91">
-        <v>4.172469247785448</v>
+        <v>4.589716172563993</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1012349359292186</v>
+        <v>0.1001101033077829</v>
       </c>
       <c r="W91">
-        <v>0.2119288021078903</v>
+        <v>0.2121940376400248</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4049397437168746</v>
+        <v>0.4004404132311314</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8914,22 +8914,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2191014676142373</v>
+        <v>0.2210014676142373</v>
       </c>
       <c r="C92">
-        <v>-319.3300111953005</v>
+        <v>-324.2404360912335</v>
       </c>
       <c r="D92">
-        <v>58.86998880469948</v>
+        <v>58.23156390876654</v>
       </c>
       <c r="E92">
-        <v>273.98</v>
+        <v>278.252</v>
       </c>
       <c r="F92">
-        <v>384.48</v>
+        <v>388.752</v>
       </c>
       <c r="G92">
         <v>6.28</v>
@@ -8950,37 +8950,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M92">
-        <v>90.66038400000001</v>
+        <v>91.66772160000001</v>
       </c>
       <c r="N92">
-        <v>-54.35630236734695</v>
+        <v>-55.36363996734695</v>
       </c>
       <c r="O92">
-        <v>-13.58907559183674</v>
+        <v>-13.84090999183674</v>
       </c>
       <c r="P92">
-        <v>-40.76722677551021</v>
+        <v>-41.52272997551021</v>
       </c>
       <c r="Q92">
-        <v>-36.86722677551021</v>
+        <v>-37.62272997551021</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2812683373821498</v>
+        <v>0.3074314859801666</v>
       </c>
       <c r="T92">
-        <v>4.589716172563993</v>
+        <v>5.099684636182215</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1001101033077829</v>
+        <v>0.0990099922824226</v>
       </c>
       <c r="W92">
-        <v>0.2121940376400248</v>
+        <v>0.2124534438198048</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4004404132311314</v>
+        <v>0.3960399691296904</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8996,22 +8996,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2210014676142373</v>
+        <v>0.2229014676142373</v>
       </c>
       <c r="C93">
-        <v>-324.2404360912335</v>
+        <v>-329.1371625427819</v>
       </c>
       <c r="D93">
-        <v>58.23156390876654</v>
+        <v>57.60683745721806</v>
       </c>
       <c r="E93">
-        <v>278.252</v>
+        <v>282.524</v>
       </c>
       <c r="F93">
-        <v>388.752</v>
+        <v>393.024</v>
       </c>
       <c r="G93">
         <v>6.28</v>
@@ -9032,37 +9032,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M93">
-        <v>91.66772160000001</v>
+        <v>92.67505920000001</v>
       </c>
       <c r="N93">
-        <v>-55.36363996734695</v>
+        <v>-56.37097756734695</v>
       </c>
       <c r="O93">
-        <v>-13.84090999183674</v>
+        <v>-14.09274439183674</v>
       </c>
       <c r="P93">
-        <v>-41.52272997551021</v>
+        <v>-42.27823317551021</v>
       </c>
       <c r="Q93">
-        <v>-37.62272997551021</v>
+        <v>-38.37823317551021</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3074314859801666</v>
+        <v>0.3401354217276875</v>
       </c>
       <c r="T93">
-        <v>5.099684636182215</v>
+        <v>5.737145215704994</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0990099922824226</v>
+        <v>0.09793379671413541</v>
       </c>
       <c r="W93">
-        <v>0.2124534438198048</v>
+        <v>0.2127072107348069</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3960399691296904</v>
+        <v>0.3917351868565416</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9078,22 +9078,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2229014676142373</v>
+        <v>0.2248014676142373</v>
       </c>
       <c r="C94">
-        <v>-329.1371625427819</v>
+        <v>-334.0206267538162</v>
       </c>
       <c r="D94">
-        <v>57.60683745721806</v>
+        <v>56.9953732461838</v>
       </c>
       <c r="E94">
-        <v>282.524</v>
+        <v>286.796</v>
       </c>
       <c r="F94">
-        <v>393.024</v>
+        <v>397.296</v>
       </c>
       <c r="G94">
         <v>6.28</v>
@@ -9114,37 +9114,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M94">
-        <v>92.67505920000001</v>
+        <v>93.68239680000001</v>
       </c>
       <c r="N94">
-        <v>-56.37097756734695</v>
+        <v>-57.37831516734695</v>
       </c>
       <c r="O94">
-        <v>-14.09274439183674</v>
+        <v>-14.34457879183674</v>
       </c>
       <c r="P94">
-        <v>-42.27823317551021</v>
+        <v>-43.03373637551021</v>
       </c>
       <c r="Q94">
-        <v>-38.37823317551021</v>
+        <v>-39.13373637551021</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3401354217276875</v>
+        <v>0.3821833391173571</v>
       </c>
       <c r="T94">
-        <v>5.737145215704994</v>
+        <v>6.556737389377137</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09793379671413541</v>
+        <v>0.09688074513656406</v>
       </c>
       <c r="W94">
-        <v>0.2127072107348069</v>
+        <v>0.2129555202967982</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3917351868565416</v>
+        <v>0.3875229805462562</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9160,22 +9160,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2248014676142373</v>
+        <v>0.2267014676142373</v>
       </c>
       <c r="C95">
-        <v>-334.0206267538162</v>
+        <v>-338.891246602488</v>
       </c>
       <c r="D95">
-        <v>56.9953732461838</v>
+        <v>56.39675339751204</v>
       </c>
       <c r="E95">
-        <v>286.796</v>
+        <v>291.068</v>
       </c>
       <c r="F95">
-        <v>397.296</v>
+        <v>401.568</v>
       </c>
       <c r="G95">
         <v>6.28</v>
@@ -9196,37 +9196,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M95">
-        <v>93.68239680000001</v>
+        <v>94.68973440000002</v>
       </c>
       <c r="N95">
-        <v>-57.37831516734695</v>
+        <v>-58.38565276734696</v>
       </c>
       <c r="O95">
-        <v>-14.34457879183674</v>
+        <v>-14.59641319183674</v>
       </c>
       <c r="P95">
-        <v>-43.03373637551021</v>
+        <v>-43.78923957551022</v>
       </c>
       <c r="Q95">
-        <v>-39.13373637551021</v>
+        <v>-39.88923957551022</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3821833391173571</v>
+        <v>0.43824722897025</v>
       </c>
       <c r="T95">
-        <v>6.556737389377137</v>
+        <v>7.649526954273327</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09688074513656406</v>
+        <v>0.09585009891170698</v>
       </c>
       <c r="W95">
-        <v>0.2129555202967982</v>
+        <v>0.2131985466766195</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3875229805462562</v>
+        <v>0.3834003956468279</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9242,22 +9242,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2267014676142373</v>
+        <v>0.2286014676142373</v>
       </c>
       <c r="C96">
-        <v>-338.891246602488</v>
+        <v>-343.7494225935988</v>
       </c>
       <c r="D96">
-        <v>56.39675339751204</v>
+        <v>55.8105774064013</v>
       </c>
       <c r="E96">
-        <v>291.068</v>
+        <v>295.34</v>
       </c>
       <c r="F96">
-        <v>401.568</v>
+        <v>405.84</v>
       </c>
       <c r="G96">
         <v>6.28</v>
@@ -9278,37 +9278,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M96">
-        <v>94.68973440000002</v>
+        <v>95.69707200000001</v>
       </c>
       <c r="N96">
-        <v>-58.38565276734696</v>
+        <v>-59.39299036734695</v>
       </c>
       <c r="O96">
-        <v>-14.59641319183674</v>
+        <v>-14.84824759183674</v>
       </c>
       <c r="P96">
-        <v>-43.78923957551022</v>
+        <v>-44.54474277551021</v>
       </c>
       <c r="Q96">
-        <v>-39.88923957551022</v>
+        <v>-40.64474277551021</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.43824722897025</v>
+        <v>0.5167366747643003</v>
       </c>
       <c r="T96">
-        <v>7.649526954273327</v>
+        <v>9.179432345127998</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09585009891170698</v>
+        <v>0.09484115050211007</v>
       </c>
       <c r="W96">
-        <v>0.2131985466766195</v>
+        <v>0.2134364567116025</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3834003956468279</v>
+        <v>0.3793646020084404</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9324,22 +9324,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2286014676142373</v>
+        <v>0.2305014676142373</v>
       </c>
       <c r="C97">
-        <v>-343.7494225935988</v>
+        <v>-348.5955387521863</v>
       </c>
       <c r="D97">
-        <v>55.8105774064013</v>
+        <v>55.23646124781372</v>
       </c>
       <c r="E97">
-        <v>295.34</v>
+        <v>299.612</v>
       </c>
       <c r="F97">
-        <v>405.84</v>
+        <v>410.112</v>
       </c>
       <c r="G97">
         <v>6.28</v>
@@ -9360,37 +9360,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M97">
-        <v>95.69707200000001</v>
+        <v>96.70440960000001</v>
       </c>
       <c r="N97">
-        <v>-59.39299036734695</v>
+        <v>-60.40032796734695</v>
       </c>
       <c r="O97">
-        <v>-14.84824759183674</v>
+        <v>-15.10008199183674</v>
       </c>
       <c r="P97">
-        <v>-44.54474277551021</v>
+        <v>-45.30024597551021</v>
       </c>
       <c r="Q97">
-        <v>-40.64474277551021</v>
+        <v>-41.40024597551021</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5167366747643003</v>
+        <v>0.6344708434553756</v>
       </c>
       <c r="T97">
-        <v>9.179432345127998</v>
+        <v>11.47429043141</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09484115050211007</v>
+        <v>0.09385322185104643</v>
       </c>
       <c r="W97">
-        <v>0.2134364567116025</v>
+        <v>0.2136694102875233</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3793646020084404</v>
+        <v>0.3754128874041858</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9406,22 +9406,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2305014676142373</v>
+        <v>0.2324014676142373</v>
       </c>
       <c r="C98">
-        <v>-348.5955387521862</v>
+        <v>-353.4299634625202</v>
       </c>
       <c r="D98">
-        <v>55.23646124781376</v>
+        <v>54.67403653747972</v>
       </c>
       <c r="E98">
-        <v>299.612</v>
+        <v>303.884</v>
       </c>
       <c r="F98">
-        <v>410.112</v>
+        <v>414.384</v>
       </c>
       <c r="G98">
         <v>6.28</v>
@@ -9442,37 +9442,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M98">
-        <v>96.70440959999999</v>
+        <v>97.71174719999999</v>
       </c>
       <c r="N98">
-        <v>-60.40032796734693</v>
+        <v>-61.40766556734693</v>
       </c>
       <c r="O98">
-        <v>-15.10008199183673</v>
+        <v>-15.35191639183673</v>
       </c>
       <c r="P98">
-        <v>-45.3002459755102</v>
+        <v>-46.0557491755102</v>
       </c>
       <c r="Q98">
-        <v>-41.4002459755102</v>
+        <v>-42.1557491755102</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6344708434553741</v>
+        <v>0.8306944579404987</v>
       </c>
       <c r="T98">
-        <v>11.47429043140997</v>
+        <v>15.29905390854663</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09385322185104644</v>
+        <v>0.09288566286289132</v>
       </c>
       <c r="W98">
-        <v>0.2136694102875233</v>
+        <v>0.2138975606969302</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3754128874041858</v>
+        <v>0.3715426514515653</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9488,22 +9488,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2324014676142373</v>
+        <v>0.2343014676142373</v>
       </c>
       <c r="C99">
-        <v>-353.4299634625202</v>
+        <v>-358.2530502563579</v>
       </c>
       <c r="D99">
-        <v>54.67403653747972</v>
+        <v>54.12294974364212</v>
       </c>
       <c r="E99">
-        <v>303.884</v>
+        <v>308.156</v>
       </c>
       <c r="F99">
-        <v>414.384</v>
+        <v>418.656</v>
       </c>
       <c r="G99">
         <v>6.28</v>
@@ -9524,37 +9524,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M99">
-        <v>97.71174719999999</v>
+        <v>98.7190848</v>
       </c>
       <c r="N99">
-        <v>-61.40766556734693</v>
+        <v>-62.41500316734695</v>
       </c>
       <c r="O99">
-        <v>-15.35191639183673</v>
+        <v>-15.60375079183674</v>
       </c>
       <c r="P99">
-        <v>-46.0557491755102</v>
+        <v>-46.81125237551021</v>
       </c>
       <c r="Q99">
-        <v>-42.1557491755102</v>
+        <v>-42.91125237551021</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8306944579404987</v>
+        <v>1.223141686910748</v>
       </c>
       <c r="T99">
-        <v>15.29905390854663</v>
+        <v>22.94858086281995</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09288566286289132</v>
+        <v>0.09193784997653529</v>
       </c>
       <c r="W99">
-        <v>0.2138975606969302</v>
+        <v>0.214121054975533</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3715426514515653</v>
+        <v>0.3677513999061411</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9570,22 +9570,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2343014676142373</v>
+        <v>0.2362014676142373</v>
       </c>
       <c r="C100">
-        <v>-358.2530502563579</v>
+        <v>-363.0651385540031</v>
       </c>
       <c r="D100">
-        <v>54.12294974364212</v>
+        <v>53.58286144599692</v>
       </c>
       <c r="E100">
-        <v>308.156</v>
+        <v>312.428</v>
       </c>
       <c r="F100">
-        <v>418.656</v>
+        <v>422.928</v>
       </c>
       <c r="G100">
         <v>6.28</v>
@@ -9606,37 +9606,37 @@
         <v>36.30408163265306</v>
       </c>
       <c r="M100">
-        <v>98.7190848</v>
+        <v>99.7264224</v>
       </c>
       <c r="N100">
-        <v>-62.41500316734695</v>
+        <v>-63.42234076734695</v>
       </c>
       <c r="O100">
-        <v>-15.60375079183674</v>
+        <v>-15.85558519183674</v>
       </c>
       <c r="P100">
-        <v>-46.81125237551021</v>
+        <v>-47.56675557551021</v>
       </c>
       <c r="Q100">
-        <v>-42.91125237551021</v>
+        <v>-43.66675557551021</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.223141686910748</v>
+        <v>2.400483373821496</v>
       </c>
       <c r="T100">
-        <v>22.94858086281995</v>
+        <v>45.89716172563989</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09193784997653529</v>
+        <v>0.09100918482525715</v>
       </c>
       <c r="W100">
-        <v>0.214121054975533</v>
+        <v>0.2143400342182044</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9644,91 +9644,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3677513999061411</v>
+        <v>0.3640367393010285</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2362014676142373</v>
-      </c>
-      <c r="C101">
-        <v>-363.0651385540031</v>
-      </c>
-      <c r="D101">
-        <v>53.58286144599692</v>
-      </c>
-      <c r="E101">
-        <v>312.428</v>
-      </c>
-      <c r="F101">
-        <v>422.928</v>
-      </c>
-      <c r="G101">
-        <v>6.28</v>
-      </c>
-      <c r="H101">
-        <v>316.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>40.20408163265306</v>
-      </c>
-      <c r="K101">
-        <v>3.899999999999999</v>
-      </c>
-      <c r="L101">
-        <v>36.30408163265306</v>
-      </c>
-      <c r="M101">
-        <v>99.7264224</v>
-      </c>
-      <c r="N101">
-        <v>-63.42234076734695</v>
-      </c>
-      <c r="O101">
-        <v>-15.85558519183674</v>
-      </c>
-      <c r="P101">
-        <v>-47.56675557551021</v>
-      </c>
-      <c r="Q101">
-        <v>-43.66675557551021</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.400483373821496</v>
-      </c>
-      <c r="T101">
-        <v>45.89716172563989</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09100918482525715</v>
-      </c>
-      <c r="W101">
-        <v>0.2143400342182044</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3640367393010285</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
